--- a/Aksiyon_Mapping_Resimli.xlsx
+++ b/Aksiyon_Mapping_Resimli.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Satis19\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Satis19\Desktop\akakce_bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1303" uniqueCount="924">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="926">
   <si>
     <t>CSS Code</t>
   </si>
@@ -2791,6 +2791,12 @@
   </si>
   <si>
     <t>https://iis-akakce.akamaized.net/p.x?https%3A%2F%2…om%2Fimages%2FI%2F51vkgUaPNbL%2E%5FSL500%5F%2Ejpg</t>
+  </si>
+  <si>
+    <t>https://www.hepsiburada.com/braun-fs1000-mini-yuz-tuy-alma-makinesi-pil-ve-temizleme-fircasi-seyahat-boy-kablosuz-kullanim-p-HBCV0000GADP9A</t>
+  </si>
+  <si>
+    <t>https://iis-akakce.akamaized.net/p.x?https%3A%2F%2…ada%2Enet%2Fs%2F777%2F600%2F110001881625381%2Ejpg</t>
   </si>
 </sst>
 </file>
@@ -3156,7 +3162,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M196"/>
+  <dimension ref="A1:M197"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
@@ -4673,13 +4679,13 @@
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
-        <v>1157621956</v>
+        <v>1639915093</v>
       </c>
       <c r="B45" s="2">
-        <v>551</v>
+        <v>1328</v>
       </c>
       <c r="C45" s="2">
-        <v>4210201313908</v>
+        <v>8006530193863</v>
       </c>
       <c r="D45" t="s">
         <v>909</v>
@@ -4687,2389 +4693,2387 @@
       <c r="E45" t="s">
         <v>224</v>
       </c>
-      <c r="F45" s="2">
-        <v>98394315</v>
-      </c>
-      <c r="G45" t="s">
-        <v>225</v>
-      </c>
-      <c r="H45" t="s">
-        <v>226</v>
-      </c>
-      <c r="I45" t="s">
-        <v>227</v>
-      </c>
-      <c r="J45" t="s">
-        <v>228</v>
-      </c>
-      <c r="K45" t="s">
-        <v>229</v>
+      <c r="F45">
+        <v>1167324802</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>924</v>
       </c>
       <c r="L45" t="s">
         <v>108</v>
       </c>
       <c r="M45" t="s">
-        <v>898</v>
+        <v>925</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
-        <v>1182520934</v>
+        <v>1157621956</v>
       </c>
       <c r="B46" s="2">
-        <v>1082</v>
+        <v>551</v>
       </c>
       <c r="C46" s="2">
-        <v>8700216554893</v>
+        <v>4210201313908</v>
       </c>
       <c r="D46" t="s">
         <v>909</v>
       </c>
       <c r="E46" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="F46" s="2">
-        <v>984960167</v>
+        <v>98394315</v>
       </c>
       <c r="G46" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="H46" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="I46" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="J46" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="K46" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="L46" t="s">
-        <v>236</v>
+        <v>108</v>
       </c>
       <c r="M46" t="s">
-        <v>237</v>
+        <v>898</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
-        <v>275958228</v>
+        <v>1182520934</v>
       </c>
       <c r="B47" s="2">
-        <v>764</v>
+        <v>1082</v>
       </c>
       <c r="C47" s="2">
-        <v>8006540914137</v>
+        <v>8700216554893</v>
       </c>
       <c r="D47" t="s">
         <v>909</v>
       </c>
       <c r="E47" t="s">
-        <v>238</v>
-      </c>
-      <c r="F47" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="F47" s="2">
+        <v>984960167</v>
+      </c>
       <c r="G47" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="H47" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="I47" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="J47" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="K47" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="L47" t="s">
         <v>236</v>
       </c>
       <c r="M47" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
-        <v>278276620</v>
-      </c>
-      <c r="B48" s="2"/>
+        <v>275958228</v>
+      </c>
+      <c r="B48" s="2">
+        <v>764</v>
+      </c>
       <c r="C48" s="2">
-        <v>7500435218078</v>
+        <v>8006540914137</v>
       </c>
       <c r="D48" t="s">
         <v>909</v>
       </c>
       <c r="E48" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="F48" s="2"/>
+      <c r="G48" t="s">
+        <v>239</v>
+      </c>
       <c r="H48" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="I48" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="J48" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="K48" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="L48" t="s">
         <v>236</v>
       </c>
       <c r="M48" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
-        <v>692404861</v>
+        <v>278276620</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" s="2">
-        <v>7500435218108</v>
+        <v>7500435218078</v>
       </c>
       <c r="D49" t="s">
         <v>909</v>
       </c>
       <c r="E49" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="F49" s="2"/>
       <c r="H49" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="I49" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="J49" t="s">
-        <v>254</v>
+        <v>248</v>
+      </c>
+      <c r="K49" t="s">
+        <v>249</v>
       </c>
       <c r="L49" t="s">
         <v>236</v>
       </c>
       <c r="M49" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
-        <v>1187410159</v>
-      </c>
-      <c r="B50" s="2">
-        <v>1089</v>
-      </c>
+        <v>692404861</v>
+      </c>
+      <c r="B50" s="2"/>
       <c r="C50" s="2">
-        <v>8700216554237</v>
+        <v>7500435218108</v>
       </c>
       <c r="D50" t="s">
         <v>909</v>
       </c>
       <c r="E50" t="s">
-        <v>256</v>
-      </c>
-      <c r="F50" s="2">
-        <v>986335511</v>
-      </c>
-      <c r="G50" t="s">
-        <v>257</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="F50" s="2"/>
       <c r="H50" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="I50" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="J50" t="s">
-        <v>260</v>
-      </c>
-      <c r="K50" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="L50" t="s">
         <v>236</v>
       </c>
       <c r="M50" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
-        <v>1187747461</v>
+        <v>1187410159</v>
       </c>
       <c r="B51" s="2">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="C51" s="2">
-        <v>8700216554404</v>
+        <v>8700216554237</v>
       </c>
       <c r="D51" t="s">
         <v>909</v>
       </c>
       <c r="E51" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="F51" s="2">
-        <v>986367531</v>
+        <v>986335511</v>
+      </c>
+      <c r="G51" t="s">
+        <v>257</v>
       </c>
       <c r="H51" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="I51" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="J51" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="K51" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="L51" t="s">
         <v>236</v>
       </c>
       <c r="M51" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
-        <v>1188084081</v>
+        <v>1187747461</v>
       </c>
       <c r="B52" s="2">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="C52" s="2">
-        <v>8700216645430</v>
+        <v>8700216554404</v>
       </c>
       <c r="D52" t="s">
         <v>909</v>
       </c>
       <c r="E52" t="s">
-        <v>269</v>
-      </c>
-      <c r="F52" s="2"/>
-      <c r="G52" t="s">
-        <v>270</v>
+        <v>263</v>
+      </c>
+      <c r="F52" s="2">
+        <v>986367531</v>
       </c>
       <c r="H52" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="I52" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="J52" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="K52" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="L52" t="s">
         <v>236</v>
       </c>
       <c r="M52" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
-        <v>1187747463</v>
+        <v>1188084081</v>
       </c>
       <c r="B53" s="2">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="C53" s="2">
-        <v>8700216645300</v>
+        <v>8700216645430</v>
       </c>
       <c r="D53" t="s">
         <v>909</v>
       </c>
       <c r="E53" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="F53" s="2"/>
+      <c r="G53" t="s">
+        <v>270</v>
+      </c>
       <c r="H53" t="s">
-        <v>277</v>
+        <v>271</v>
+      </c>
+      <c r="I53" t="s">
+        <v>272</v>
+      </c>
+      <c r="J53" t="s">
+        <v>273</v>
+      </c>
+      <c r="K53" t="s">
+        <v>274</v>
       </c>
       <c r="L53" t="s">
         <v>236</v>
       </c>
       <c r="M53" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
-        <v>1187747462</v>
+        <v>1187747463</v>
       </c>
       <c r="B54" s="2">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="C54" s="2">
-        <v>8700216644907</v>
+        <v>8700216645300</v>
       </c>
       <c r="D54" t="s">
         <v>909</v>
       </c>
       <c r="E54" t="s">
-        <v>279</v>
-      </c>
-      <c r="F54" s="2">
-        <v>986470107</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="F54" s="2"/>
       <c r="H54" t="s">
-        <v>280</v>
-      </c>
-      <c r="I54" t="s">
-        <v>281</v>
-      </c>
-      <c r="J54" t="s">
-        <v>282</v>
-      </c>
-      <c r="K54" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="L54" t="s">
         <v>236</v>
       </c>
       <c r="M54" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
-        <v>1208259392</v>
+        <v>1187747462</v>
       </c>
       <c r="B55" s="2">
-        <v>1098</v>
+        <v>1085</v>
       </c>
       <c r="C55" s="2">
-        <v>8700216916738</v>
+        <v>8700216644907</v>
       </c>
       <c r="D55" t="s">
         <v>909</v>
       </c>
       <c r="E55" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="F55" s="2">
-        <v>992270628</v>
-      </c>
-      <c r="G55" t="s">
-        <v>286</v>
+        <v>986470107</v>
       </c>
       <c r="H55" t="s">
-        <v>287</v>
+        <v>280</v>
+      </c>
+      <c r="I55" t="s">
+        <v>281</v>
+      </c>
+      <c r="J55" t="s">
+        <v>282</v>
+      </c>
+      <c r="K55" t="s">
+        <v>283</v>
       </c>
       <c r="L55" t="s">
         <v>236</v>
       </c>
       <c r="M55" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
-        <v>1187747460</v>
+        <v>1208259392</v>
       </c>
       <c r="B56" s="2">
-        <v>1091</v>
+        <v>1098</v>
       </c>
       <c r="C56" s="2">
-        <v>8700216646130</v>
+        <v>8700216916738</v>
       </c>
       <c r="D56" t="s">
         <v>909</v>
       </c>
       <c r="E56" t="s">
-        <v>289</v>
-      </c>
-      <c r="F56" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="F56" s="2">
+        <v>992270628</v>
+      </c>
       <c r="G56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="H56" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="L56" t="s">
         <v>236</v>
       </c>
       <c r="M56" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
-        <v>1182635821</v>
+        <v>1187747460</v>
       </c>
       <c r="B57" s="2">
-        <v>1083</v>
+        <v>1091</v>
       </c>
       <c r="C57" s="2">
-        <v>8700216645935</v>
+        <v>8700216646130</v>
       </c>
       <c r="D57" t="s">
         <v>909</v>
       </c>
       <c r="E57" t="s">
-        <v>293</v>
-      </c>
-      <c r="F57" s="2">
-        <v>984959968</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="F57" s="2"/>
       <c r="G57" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="H57" t="s">
-        <v>295</v>
-      </c>
-      <c r="I57" t="s">
-        <v>296</v>
-      </c>
-      <c r="J57" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="L57" t="s">
         <v>236</v>
       </c>
       <c r="M57" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
-        <v>1206932099</v>
+        <v>1182635821</v>
       </c>
       <c r="B58" s="2">
-        <v>1097</v>
+        <v>1083</v>
       </c>
       <c r="C58" s="2">
-        <v>8700216645782</v>
+        <v>8700216645935</v>
       </c>
       <c r="D58" t="s">
         <v>909</v>
       </c>
       <c r="E58" t="s">
-        <v>299</v>
-      </c>
-      <c r="F58" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="F58" s="2">
+        <v>984959968</v>
+      </c>
+      <c r="G58" t="s">
+        <v>294</v>
+      </c>
       <c r="H58" t="s">
-        <v>300</v>
+        <v>295</v>
+      </c>
+      <c r="I58" t="s">
+        <v>296</v>
       </c>
       <c r="J58" t="s">
-        <v>301</v>
-      </c>
-      <c r="K58" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="L58" t="s">
         <v>236</v>
       </c>
       <c r="M58" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
-        <v>1187747459</v>
+        <v>1206932099</v>
       </c>
       <c r="B59" s="2">
-        <v>1086</v>
+        <v>1097</v>
       </c>
       <c r="C59" s="2">
-        <v>8700216645522</v>
+        <v>8700216645782</v>
       </c>
       <c r="D59" t="s">
         <v>909</v>
       </c>
       <c r="E59" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="F59" s="2"/>
-      <c r="G59" t="s">
-        <v>305</v>
-      </c>
       <c r="H59" t="s">
-        <v>306</v>
+        <v>300</v>
+      </c>
+      <c r="J59" t="s">
+        <v>301</v>
+      </c>
+      <c r="K59" t="s">
+        <v>302</v>
       </c>
       <c r="L59" t="s">
         <v>236</v>
       </c>
       <c r="M59" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
-        <v>54907093</v>
+        <v>1187747459</v>
       </c>
       <c r="B60" s="2">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="C60" s="2">
-        <v>8700216735568</v>
+        <v>8700216645522</v>
       </c>
       <c r="D60" t="s">
         <v>909</v>
       </c>
       <c r="E60" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="F60" s="2"/>
+      <c r="G60" t="s">
+        <v>305</v>
+      </c>
       <c r="H60" t="s">
-        <v>309</v>
-      </c>
-      <c r="I60" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="L60" t="s">
         <v>236</v>
       </c>
       <c r="M60" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
-        <v>53769528</v>
+        <v>54907093</v>
       </c>
       <c r="B61" s="2">
-        <v>1114</v>
+        <v>1084</v>
       </c>
       <c r="C61" s="2">
-        <v>4210201163305</v>
+        <v>8700216735568</v>
       </c>
       <c r="D61" t="s">
         <v>909</v>
       </c>
       <c r="E61" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="F61" s="2"/>
       <c r="H61" t="s">
-        <v>313</v>
-      </c>
-      <c r="K61" t="s">
-        <v>314</v>
+        <v>309</v>
+      </c>
+      <c r="I61" t="s">
+        <v>310</v>
       </c>
       <c r="L61" t="s">
         <v>236</v>
       </c>
       <c r="M61" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
-        <v>68494393</v>
+        <v>53769528</v>
       </c>
       <c r="B62" s="2">
-        <v>1096</v>
+        <v>1114</v>
       </c>
       <c r="C62" s="2">
-        <v>8700216735667</v>
+        <v>4210201163305</v>
       </c>
       <c r="D62" t="s">
         <v>909</v>
       </c>
       <c r="E62" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="F62" s="2"/>
-      <c r="G62" t="s">
-        <v>317</v>
-      </c>
       <c r="H62" t="s">
-        <v>318</v>
-      </c>
-      <c r="I62" t="s">
-        <v>319</v>
+        <v>313</v>
+      </c>
+      <c r="K62" t="s">
+        <v>314</v>
       </c>
       <c r="L62" t="s">
         <v>236</v>
       </c>
       <c r="M62" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
-        <v>681887915</v>
+        <v>68494393</v>
       </c>
       <c r="B63" s="2">
-        <v>1104</v>
+        <v>1096</v>
       </c>
       <c r="C63" s="2">
-        <v>8700216735940</v>
+        <v>8700216735667</v>
       </c>
       <c r="D63" t="s">
         <v>909</v>
       </c>
       <c r="E63" t="s">
-        <v>321</v>
-      </c>
-      <c r="F63" s="2">
-        <v>1016895529</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="F63" s="2"/>
       <c r="G63" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="H63" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="I63" t="s">
-        <v>324</v>
-      </c>
-      <c r="J63" t="s">
-        <v>325</v>
-      </c>
-      <c r="K63" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="L63" t="s">
         <v>236</v>
       </c>
       <c r="M63" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
-        <v>1114746994</v>
+        <v>681887915</v>
       </c>
       <c r="B64" s="2">
-        <v>1063</v>
+        <v>1104</v>
       </c>
       <c r="C64" s="2">
-        <v>8700216429023</v>
+        <v>8700216735940</v>
       </c>
       <c r="D64" t="s">
         <v>909</v>
       </c>
       <c r="E64" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="F64" s="2">
-        <v>954828544</v>
+        <v>1016895529</v>
       </c>
       <c r="G64" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="H64" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="I64" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="J64" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="K64" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="L64" t="s">
-        <v>334</v>
+        <v>236</v>
       </c>
       <c r="M64" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
-        <v>1114747113</v>
+        <v>1114746994</v>
       </c>
       <c r="B65" s="2">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="C65" s="2">
-        <v>8700216429030</v>
+        <v>8700216429023</v>
       </c>
       <c r="D65" t="s">
         <v>909</v>
       </c>
       <c r="E65" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="F65" s="2">
-        <v>954826148</v>
+        <v>954828544</v>
       </c>
       <c r="G65" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="H65" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="I65" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="J65" t="s">
-        <v>340</v>
+        <v>332</v>
+      </c>
+      <c r="K65" t="s">
+        <v>333</v>
       </c>
       <c r="L65" t="s">
         <v>334</v>
       </c>
       <c r="M65" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
-        <v>1114543461</v>
+        <v>1114747113</v>
       </c>
       <c r="B66" s="2">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="C66" s="2">
-        <v>8700216429016</v>
+        <v>8700216429030</v>
       </c>
       <c r="D66" t="s">
         <v>909</v>
       </c>
       <c r="E66" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="F66" s="2">
-        <v>954818310</v>
+        <v>954826148</v>
       </c>
       <c r="G66" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="H66" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="I66" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="J66" t="s">
-        <v>346</v>
-      </c>
-      <c r="K66" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="L66" t="s">
         <v>334</v>
       </c>
       <c r="M66" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
-        <v>1114791277</v>
+        <v>1114543461</v>
       </c>
       <c r="B67" s="2">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="C67" s="2">
-        <v>8700216429238</v>
+        <v>8700216429016</v>
       </c>
       <c r="D67" t="s">
         <v>909</v>
       </c>
       <c r="E67" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="F67" s="2">
-        <v>954819173</v>
+        <v>954818310</v>
       </c>
       <c r="G67" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="H67" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="I67" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="J67" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="K67" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="L67" t="s">
         <v>334</v>
       </c>
       <c r="M67" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
-        <v>1113690594</v>
+        <v>1114791277</v>
       </c>
       <c r="B68" s="2">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="C68" s="2">
-        <v>8700216429504</v>
+        <v>8700216429238</v>
       </c>
       <c r="D68" t="s">
         <v>909</v>
       </c>
       <c r="E68" t="s">
-        <v>356</v>
-      </c>
-      <c r="F68" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="F68" s="2">
+        <v>954819173</v>
+      </c>
       <c r="G68" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="H68" t="s">
-        <v>358</v>
+        <v>351</v>
+      </c>
+      <c r="I68" t="s">
+        <v>352</v>
+      </c>
+      <c r="J68" t="s">
+        <v>353</v>
+      </c>
+      <c r="K68" t="s">
+        <v>354</v>
       </c>
       <c r="L68" t="s">
         <v>334</v>
       </c>
       <c r="M68" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
-        <v>1114800910</v>
+        <v>1113690594</v>
       </c>
       <c r="B69" s="2">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="C69" s="2">
-        <v>8700216429160</v>
+        <v>8700216429504</v>
       </c>
       <c r="D69" t="s">
         <v>909</v>
       </c>
       <c r="E69" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="F69" s="2"/>
+      <c r="G69" t="s">
+        <v>357</v>
+      </c>
       <c r="H69" t="s">
-        <v>361</v>
-      </c>
-      <c r="I69" t="s">
-        <v>362</v>
-      </c>
-      <c r="J69" t="s">
-        <v>363</v>
-      </c>
-      <c r="K69" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="L69" t="s">
         <v>334</v>
       </c>
       <c r="M69" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
-        <v>1113503174</v>
+        <v>1114800910</v>
       </c>
       <c r="B70" s="2">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="C70" s="2">
-        <v>8700216429306</v>
+        <v>8700216429160</v>
       </c>
       <c r="D70" t="s">
         <v>909</v>
       </c>
       <c r="E70" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="F70" s="2"/>
-      <c r="G70" t="s">
-        <v>367</v>
-      </c>
       <c r="H70" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="I70" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="J70" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="K70" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="L70" t="s">
         <v>334</v>
       </c>
       <c r="M70" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
-        <v>1114153742</v>
+        <v>1113503174</v>
       </c>
       <c r="B71" s="2">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="C71" s="2">
-        <v>8700216429337</v>
+        <v>8700216429306</v>
       </c>
       <c r="D71" t="s">
         <v>909</v>
       </c>
       <c r="E71" t="s">
-        <v>373</v>
-      </c>
-      <c r="F71" s="2">
-        <v>954752198</v>
+        <v>366</v>
+      </c>
+      <c r="F71" s="2"/>
+      <c r="G71" t="s">
+        <v>367</v>
       </c>
       <c r="H71" t="s">
-        <v>374</v>
+        <v>368</v>
+      </c>
+      <c r="I71" t="s">
+        <v>369</v>
+      </c>
+      <c r="J71" t="s">
+        <v>370</v>
+      </c>
+      <c r="K71" t="s">
+        <v>371</v>
       </c>
       <c r="L71" t="s">
         <v>334</v>
       </c>
       <c r="M71" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
-        <v>1114781151</v>
+        <v>1114153742</v>
       </c>
       <c r="B72" s="2">
-        <v>1072</v>
+        <v>1057</v>
       </c>
       <c r="C72" s="2">
-        <v>4987176251060</v>
+        <v>8700216429337</v>
       </c>
       <c r="D72" t="s">
         <v>909</v>
       </c>
       <c r="E72" t="s">
-        <v>376</v>
-      </c>
-      <c r="F72" s="2"/>
-      <c r="G72" t="s">
-        <v>377</v>
+        <v>373</v>
+      </c>
+      <c r="F72" s="2">
+        <v>954752198</v>
       </c>
       <c r="H72" t="s">
-        <v>378</v>
-      </c>
-      <c r="I72" t="s">
-        <v>379</v>
-      </c>
-      <c r="K72" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="L72" t="s">
         <v>334</v>
       </c>
       <c r="M72" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
-        <v>1114792532</v>
+        <v>1114781151</v>
       </c>
       <c r="B73" s="2">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="C73" s="2">
-        <v>4987176251046</v>
+        <v>4987176251060</v>
       </c>
       <c r="D73" t="s">
         <v>909</v>
       </c>
       <c r="E73" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="F73" s="2"/>
+      <c r="G73" t="s">
+        <v>377</v>
+      </c>
       <c r="H73" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="I73" t="s">
-        <v>384</v>
-      </c>
-      <c r="J73" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="K73" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="L73" t="s">
         <v>334</v>
       </c>
       <c r="M73" t="s">
-        <v>899</v>
+        <v>381</v>
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
-        <v>1114770946</v>
+        <v>1114792532</v>
       </c>
       <c r="B74" s="2">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="C74" s="2">
-        <v>8700216427715</v>
+        <v>4987176251046</v>
       </c>
       <c r="D74" t="s">
         <v>909</v>
       </c>
       <c r="E74" t="s">
-        <v>387</v>
-      </c>
-      <c r="F74" s="2">
-        <v>955101547</v>
-      </c>
-      <c r="G74" t="s">
-        <v>388</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="F74" s="2"/>
       <c r="H74" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="I74" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="J74" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="K74" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="L74" t="s">
         <v>334</v>
       </c>
       <c r="M74" t="s">
-        <v>393</v>
+        <v>899</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
-        <v>1114773030</v>
+        <v>1114770946</v>
       </c>
       <c r="B75" s="2">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="C75" s="2">
-        <v>8700216428415</v>
+        <v>8700216427715</v>
       </c>
       <c r="D75" t="s">
         <v>909</v>
       </c>
       <c r="E75" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="F75" s="2">
-        <v>955008747</v>
+        <v>955101547</v>
       </c>
       <c r="G75" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="H75" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="I75" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="J75" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="K75" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="L75" t="s">
         <v>334</v>
       </c>
       <c r="M75" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
-        <v>1133524245</v>
+        <v>1114773030</v>
       </c>
       <c r="B76" s="2">
-        <v>1075</v>
+        <v>1070</v>
       </c>
       <c r="C76" s="2">
-        <v>8700216428422</v>
+        <v>8700216428415</v>
       </c>
       <c r="D76" t="s">
         <v>909</v>
       </c>
       <c r="E76" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="F76" s="2">
-        <v>960743916</v>
+        <v>955008747</v>
       </c>
       <c r="G76" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="H76" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="I76" t="s">
-        <v>404</v>
+        <v>397</v>
+      </c>
+      <c r="J76" t="s">
+        <v>398</v>
       </c>
       <c r="K76" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="L76" t="s">
         <v>334</v>
       </c>
       <c r="M76" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
-        <v>1114800920</v>
+        <v>1133524245</v>
       </c>
       <c r="B77" s="2">
-        <v>1068</v>
+        <v>1075</v>
       </c>
       <c r="C77" s="2">
-        <v>8700216427906</v>
+        <v>8700216428422</v>
       </c>
       <c r="D77" t="s">
         <v>909</v>
       </c>
       <c r="E77" t="s">
-        <v>407</v>
-      </c>
-      <c r="F77" s="2"/>
+        <v>401</v>
+      </c>
+      <c r="F77" s="2">
+        <v>960743916</v>
+      </c>
       <c r="G77" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="H77" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="I77" t="s">
-        <v>410</v>
-      </c>
-      <c r="J77" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="K77" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="L77" t="s">
         <v>334</v>
       </c>
       <c r="M77" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
-        <v>1114817642</v>
+        <v>1114800920</v>
       </c>
       <c r="B78" s="2">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="C78" s="2">
-        <v>8700216428002</v>
+        <v>8700216427906</v>
       </c>
       <c r="D78" t="s">
         <v>909</v>
       </c>
       <c r="E78" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="F78" s="2"/>
+      <c r="G78" t="s">
+        <v>408</v>
+      </c>
       <c r="H78" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="I78" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="J78" t="s">
-        <v>417</v>
+        <v>411</v>
+      </c>
+      <c r="K78" t="s">
+        <v>412</v>
       </c>
       <c r="L78" t="s">
         <v>334</v>
       </c>
       <c r="M78" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
-        <v>1118925559</v>
+        <v>1114817642</v>
       </c>
       <c r="B79" s="2">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="C79" s="2">
-        <v>8700216427098</v>
+        <v>8700216428002</v>
       </c>
       <c r="D79" t="s">
         <v>909</v>
       </c>
       <c r="E79" t="s">
-        <v>419</v>
-      </c>
-      <c r="F79" s="2">
-        <v>955168203</v>
-      </c>
-      <c r="G79" t="s">
-        <v>420</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="F79" s="2"/>
       <c r="H79" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="I79" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="J79" t="s">
-        <v>423</v>
-      </c>
-      <c r="K79" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="L79" t="s">
         <v>334</v>
       </c>
       <c r="M79" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
-        <v>1118928127</v>
+        <v>1118925559</v>
       </c>
       <c r="B80" s="2">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="C80" s="2">
-        <v>8700216427319</v>
+        <v>8700216427098</v>
       </c>
       <c r="D80" t="s">
         <v>909</v>
       </c>
       <c r="E80" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="F80" s="2">
-        <v>954934176</v>
+        <v>955168203</v>
       </c>
       <c r="G80" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="H80" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="I80" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="J80" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="K80" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="L80" t="s">
         <v>334</v>
       </c>
       <c r="M80" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
-        <v>1118925552</v>
+        <v>1118928127</v>
       </c>
       <c r="B81" s="2">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="C81" s="2">
-        <v>8700216427272</v>
+        <v>8700216427319</v>
       </c>
       <c r="D81" t="s">
         <v>909</v>
       </c>
       <c r="E81" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="F81" s="2">
-        <v>954871389</v>
+        <v>954934176</v>
       </c>
       <c r="G81" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="H81" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="I81" t="s">
-        <v>436</v>
+        <v>429</v>
+      </c>
+      <c r="J81" t="s">
+        <v>430</v>
+      </c>
+      <c r="K81" t="s">
+        <v>431</v>
       </c>
       <c r="L81" t="s">
         <v>334</v>
       </c>
       <c r="M81" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
-        <v>1118928411</v>
+        <v>1118925552</v>
       </c>
       <c r="B82" s="2">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="C82" s="2">
-        <v>8700216427241</v>
+        <v>8700216427272</v>
       </c>
       <c r="D82" t="s">
         <v>909</v>
       </c>
       <c r="E82" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="F82" s="2">
-        <v>954752198</v>
+        <v>954871389</v>
       </c>
       <c r="G82" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="H82" t="s">
-        <v>440</v>
-      </c>
-      <c r="J82" t="s">
-        <v>441</v>
-      </c>
-      <c r="K82" t="s">
-        <v>442</v>
+        <v>435</v>
+      </c>
+      <c r="I82" t="s">
+        <v>436</v>
       </c>
       <c r="L82" t="s">
         <v>334</v>
       </c>
       <c r="M82" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
-        <v>1200121151</v>
+        <v>1118928411</v>
       </c>
       <c r="B83" s="2">
-        <v>1094</v>
+        <v>1065</v>
       </c>
       <c r="C83" s="2">
-        <v>8700216555562</v>
+        <v>8700216427241</v>
       </c>
       <c r="D83" t="s">
         <v>909</v>
       </c>
       <c r="E83" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="F83" s="2">
-        <v>991027947</v>
+        <v>954752198</v>
       </c>
       <c r="G83" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="H83" t="s">
-        <v>446</v>
-      </c>
-      <c r="I83" t="s">
-        <v>447</v>
+        <v>440</v>
+      </c>
+      <c r="J83" t="s">
+        <v>441</v>
+      </c>
+      <c r="K83" t="s">
+        <v>442</v>
       </c>
       <c r="L83" t="s">
-        <v>448</v>
+        <v>334</v>
       </c>
       <c r="M83" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
-        <v>198421057</v>
+        <v>1200121151</v>
       </c>
       <c r="B84" s="2">
-        <v>914</v>
+        <v>1094</v>
       </c>
       <c r="C84" s="2">
-        <v>4210201394792</v>
+        <v>8700216555562</v>
       </c>
       <c r="D84" t="s">
         <v>909</v>
       </c>
       <c r="E84" t="s">
-        <v>450</v>
-      </c>
-      <c r="F84" s="2"/>
+        <v>444</v>
+      </c>
+      <c r="F84" s="2">
+        <v>991027947</v>
+      </c>
+      <c r="G84" t="s">
+        <v>445</v>
+      </c>
       <c r="H84" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="I84" t="s">
-        <v>452</v>
-      </c>
-      <c r="J84" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="L84" t="s">
         <v>448</v>
       </c>
       <c r="M84" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
-        <v>786336845</v>
+        <v>198421057</v>
       </c>
       <c r="B85" s="2">
-        <v>946</v>
+        <v>914</v>
       </c>
       <c r="C85" s="2">
-        <v>8006540985199</v>
+        <v>4210201394792</v>
       </c>
       <c r="D85" t="s">
         <v>909</v>
       </c>
       <c r="E85" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="F85" s="2"/>
-      <c r="G85" t="s">
-        <v>456</v>
-      </c>
       <c r="H85" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="I85" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="J85" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="L85" t="s">
         <v>448</v>
       </c>
       <c r="M85" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
-        <v>1234216667</v>
+        <v>786336845</v>
       </c>
       <c r="B86" s="2">
-        <v>1107</v>
+        <v>946</v>
       </c>
       <c r="C86" s="2">
-        <v>4987176189066</v>
+        <v>8006540985199</v>
       </c>
       <c r="D86" t="s">
         <v>909</v>
       </c>
       <c r="E86" t="s">
-        <v>461</v>
-      </c>
-      <c r="F86" s="2">
-        <v>1019092116</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="F86" s="2"/>
       <c r="G86" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="H86" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="I86" t="s">
-        <v>464</v>
+        <v>458</v>
+      </c>
+      <c r="J86" t="s">
+        <v>459</v>
       </c>
       <c r="L86" t="s">
         <v>448</v>
       </c>
       <c r="M86" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
-        <v>1150800873</v>
+        <v>1234216667</v>
       </c>
       <c r="B87" s="2">
-        <v>918</v>
+        <v>1107</v>
       </c>
       <c r="C87" s="2">
-        <v>4210201262916</v>
+        <v>4987176189066</v>
       </c>
       <c r="D87" t="s">
         <v>909</v>
       </c>
       <c r="E87" t="s">
-        <v>466</v>
-      </c>
-      <c r="F87" s="2"/>
+        <v>461</v>
+      </c>
+      <c r="F87" s="2">
+        <v>1019092116</v>
+      </c>
       <c r="G87" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="H87" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="I87" t="s">
-        <v>469</v>
-      </c>
-      <c r="J87" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="L87" t="s">
         <v>448</v>
       </c>
       <c r="M87" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
-        <v>100488934</v>
-      </c>
-      <c r="B88" s="2"/>
+        <v>1150800873</v>
+      </c>
+      <c r="B88" s="2">
+        <v>918</v>
+      </c>
       <c r="C88" s="2">
-        <v>4210201072942</v>
+        <v>4210201262916</v>
       </c>
       <c r="D88" t="s">
         <v>909</v>
       </c>
       <c r="E88" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="F88" s="2"/>
+      <c r="G88" t="s">
+        <v>467</v>
+      </c>
       <c r="H88" t="s">
-        <v>473</v>
+        <v>468</v>
+      </c>
+      <c r="I88" t="s">
+        <v>469</v>
+      </c>
+      <c r="J88" t="s">
+        <v>470</v>
       </c>
       <c r="L88" t="s">
         <v>448</v>
       </c>
       <c r="M88" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
-        <v>1156458962</v>
-      </c>
-      <c r="B89" s="2">
-        <v>1077</v>
-      </c>
+        <v>100488934</v>
+      </c>
+      <c r="B89" s="2"/>
       <c r="C89" s="2">
-        <v>8700216051330</v>
+        <v>4210201072942</v>
       </c>
       <c r="D89" t="s">
         <v>909</v>
       </c>
       <c r="E89" t="s">
-        <v>475</v>
-      </c>
-      <c r="F89" s="2">
-        <v>971213503</v>
-      </c>
-      <c r="G89" t="s">
-        <v>476</v>
-      </c>
+        <v>472</v>
+      </c>
+      <c r="F89" s="2"/>
       <c r="H89" t="s">
-        <v>477</v>
-      </c>
-      <c r="I89" t="s">
-        <v>478</v>
-      </c>
-      <c r="J89" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="L89" t="s">
         <v>448</v>
       </c>
       <c r="M89" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
-        <v>680062120</v>
+        <v>1156458962</v>
       </c>
       <c r="B90" s="2">
-        <v>996</v>
+        <v>1077</v>
       </c>
       <c r="C90" s="2">
-        <v>4210201072195</v>
+        <v>8700216051330</v>
       </c>
       <c r="D90" t="s">
         <v>909</v>
       </c>
       <c r="E90" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="F90" s="2">
-        <v>281398</v>
+        <v>971213503</v>
       </c>
       <c r="G90" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="H90" t="s">
-        <v>483</v>
+        <v>477</v>
+      </c>
+      <c r="I90" t="s">
+        <v>478</v>
       </c>
       <c r="J90" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="L90" t="s">
         <v>448</v>
       </c>
       <c r="M90" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
-        <v>453459619</v>
+        <v>680062120</v>
       </c>
       <c r="B91" s="2">
-        <v>1095</v>
+        <v>996</v>
       </c>
       <c r="C91" s="2">
-        <v>8700216735797</v>
+        <v>4210201072195</v>
       </c>
       <c r="D91" t="s">
         <v>909</v>
       </c>
       <c r="E91" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="F91" s="2">
-        <v>991027833</v>
+        <v>281398</v>
       </c>
       <c r="G91" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="H91" t="s">
-        <v>488</v>
-      </c>
-      <c r="I91" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="J91" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="L91" t="s">
         <v>448</v>
       </c>
       <c r="M91" t="s">
-        <v>900</v>
+        <v>485</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
-        <v>1252178966</v>
-      </c>
-      <c r="B92" s="2"/>
+        <v>453459619</v>
+      </c>
+      <c r="B92" s="2">
+        <v>1095</v>
+      </c>
       <c r="C92" s="2">
-        <v>4210201163626</v>
+        <v>8700216735797</v>
       </c>
       <c r="D92" t="s">
         <v>909</v>
       </c>
       <c r="E92" t="s">
-        <v>491</v>
-      </c>
-      <c r="F92" s="2"/>
+        <v>486</v>
+      </c>
+      <c r="F92" s="2">
+        <v>991027833</v>
+      </c>
+      <c r="G92" t="s">
+        <v>487</v>
+      </c>
       <c r="H92" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="I92" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="J92" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="L92" t="s">
         <v>448</v>
       </c>
       <c r="M92" t="s">
-        <v>495</v>
+        <v>900</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
-        <v>1543524</v>
-      </c>
-      <c r="B93" s="2">
-        <v>104</v>
-      </c>
+        <v>1252178966</v>
+      </c>
+      <c r="B93" s="2"/>
       <c r="C93" s="2">
-        <v>3030050182125</v>
+        <v>4210201163626</v>
       </c>
       <c r="D93" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="E93" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="F93" s="2"/>
       <c r="H93" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="I93" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="J93" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="L93" t="s">
-        <v>500</v>
+        <v>448</v>
       </c>
       <c r="M93" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
-        <v>10991</v>
+        <v>1543524</v>
       </c>
       <c r="B94" s="2">
-        <v>202</v>
+        <v>104</v>
       </c>
       <c r="C94" s="2">
-        <v>3030050182163</v>
+        <v>3030050182125</v>
       </c>
       <c r="D94" t="s">
         <v>910</v>
       </c>
       <c r="E94" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="F94" s="2"/>
-      <c r="G94" t="s">
-        <v>503</v>
-      </c>
       <c r="H94" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="I94" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="J94" t="s">
-        <v>506</v>
-      </c>
-      <c r="K94" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="L94" t="s">
         <v>500</v>
       </c>
       <c r="M94" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
-        <v>651275887</v>
+        <v>10991</v>
       </c>
       <c r="B95" s="2">
-        <v>861</v>
+        <v>202</v>
       </c>
       <c r="C95" s="2">
-        <v>3030050188950</v>
+        <v>3030050182163</v>
       </c>
       <c r="D95" t="s">
         <v>910</v>
       </c>
       <c r="E95" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="F95" s="2"/>
       <c r="G95" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="H95" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="I95" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="J95" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="K95" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="L95" t="s">
-        <v>515</v>
+        <v>500</v>
       </c>
       <c r="M95" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
-        <v>652166918</v>
+        <v>651275887</v>
       </c>
       <c r="B96" s="2">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="C96" s="2">
-        <v>3030050188943</v>
+        <v>3030050188950</v>
       </c>
       <c r="D96" t="s">
         <v>910</v>
       </c>
       <c r="E96" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="F96" s="2"/>
       <c r="G96" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="H96" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="I96" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="J96" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="K96" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="L96" t="s">
         <v>515</v>
       </c>
       <c r="M96" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
-        <v>1221179552</v>
+        <v>652166918</v>
       </c>
       <c r="B97" s="2">
-        <v>1105</v>
+        <v>862</v>
       </c>
       <c r="C97" s="2">
-        <v>3030050197556</v>
+        <v>3030050188943</v>
       </c>
       <c r="D97" t="s">
         <v>910</v>
       </c>
       <c r="E97" t="s">
-        <v>524</v>
-      </c>
-      <c r="F97" s="2">
-        <v>996351410</v>
+        <v>517</v>
+      </c>
+      <c r="F97" s="2"/>
+      <c r="G97" t="s">
+        <v>518</v>
       </c>
       <c r="H97" t="s">
-        <v>525</v>
+        <v>519</v>
+      </c>
+      <c r="I97" t="s">
+        <v>520</v>
+      </c>
+      <c r="J97" t="s">
+        <v>521</v>
+      </c>
+      <c r="K97" t="s">
+        <v>522</v>
       </c>
       <c r="L97" t="s">
         <v>515</v>
       </c>
       <c r="M97" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
-        <v>1501001171</v>
+        <v>1221179552</v>
       </c>
       <c r="B98" s="2">
-        <v>1298</v>
+        <v>1105</v>
       </c>
       <c r="C98" s="2">
-        <v>3030050197549</v>
+        <v>3030050197556</v>
       </c>
       <c r="D98" t="s">
         <v>910</v>
       </c>
       <c r="E98" t="s">
-        <v>527</v>
-      </c>
-      <c r="F98" s="2"/>
+        <v>524</v>
+      </c>
+      <c r="F98" s="2">
+        <v>996351410</v>
+      </c>
       <c r="H98" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="L98" t="s">
         <v>515</v>
       </c>
       <c r="M98" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
-        <v>1221179553</v>
+        <v>1501001171</v>
       </c>
       <c r="B99" s="2">
-        <v>1106</v>
+        <v>1298</v>
       </c>
       <c r="C99" s="2">
-        <v>3030050197532</v>
+        <v>3030050197549</v>
       </c>
       <c r="D99" t="s">
         <v>910</v>
       </c>
       <c r="E99" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="F99" s="2"/>
       <c r="H99" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="L99" t="s">
         <v>515</v>
       </c>
       <c r="M99" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
-        <v>1279299255</v>
+        <v>1221179553</v>
       </c>
       <c r="B100" s="2">
-        <v>1118</v>
+        <v>1106</v>
       </c>
       <c r="C100" s="2">
-        <v>3030050197525</v>
+        <v>3030050197532</v>
       </c>
       <c r="D100" t="s">
         <v>910</v>
       </c>
       <c r="E100" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="F100" s="2"/>
       <c r="H100" t="s">
-        <v>534</v>
-      </c>
-      <c r="I100" t="s">
-        <v>535</v>
-      </c>
-      <c r="J100" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="L100" t="s">
         <v>515</v>
       </c>
       <c r="M100" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
-        <v>1279731477</v>
+        <v>1279299255</v>
       </c>
       <c r="B101" s="2">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="C101" s="2">
-        <v>3030050197518</v>
+        <v>3030050197525</v>
       </c>
       <c r="D101" t="s">
         <v>910</v>
       </c>
       <c r="E101" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="F101" s="2"/>
       <c r="H101" t="s">
-        <v>539</v>
+        <v>534</v>
+      </c>
+      <c r="I101" t="s">
+        <v>535</v>
+      </c>
+      <c r="J101" t="s">
+        <v>536</v>
       </c>
       <c r="L101" t="s">
         <v>515</v>
       </c>
       <c r="M101" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
-        <v>1279299260</v>
+        <v>1279731477</v>
       </c>
       <c r="B102" s="2">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="C102" s="2">
-        <v>3030050197570</v>
+        <v>3030050197518</v>
       </c>
       <c r="D102" t="s">
         <v>910</v>
       </c>
       <c r="E102" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="F102" s="2"/>
       <c r="H102" t="s">
-        <v>542</v>
-      </c>
-      <c r="I102" t="s">
-        <v>543</v>
-      </c>
-      <c r="J102" t="s">
-        <v>544</v>
-      </c>
-      <c r="K102" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="L102" t="s">
-        <v>546</v>
+        <v>515</v>
       </c>
       <c r="M102" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
-        <v>1279731445</v>
+        <v>1279299260</v>
       </c>
       <c r="B103" s="2">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C103" s="2">
-        <v>3030050197587</v>
+        <v>3030050197570</v>
       </c>
       <c r="D103" t="s">
         <v>910</v>
       </c>
       <c r="E103" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="F103" s="2"/>
-      <c r="G103" t="s">
-        <v>549</v>
-      </c>
       <c r="H103" t="s">
-        <v>550</v>
+        <v>542</v>
+      </c>
+      <c r="I103" t="s">
+        <v>543</v>
+      </c>
+      <c r="J103" t="s">
+        <v>544</v>
+      </c>
+      <c r="K103" t="s">
+        <v>545</v>
       </c>
       <c r="L103" t="s">
         <v>546</v>
       </c>
       <c r="M103" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
-        <v>1214135337</v>
+        <v>1279731445</v>
       </c>
       <c r="B104" s="2">
-        <v>1099</v>
+        <v>1115</v>
       </c>
       <c r="C104" s="2">
-        <v>3030050197594</v>
+        <v>3030050197587</v>
       </c>
       <c r="D104" t="s">
         <v>910</v>
       </c>
       <c r="E104" t="s">
-        <v>552</v>
-      </c>
-      <c r="F104" s="2">
-        <v>995633087</v>
+        <v>548</v>
+      </c>
+      <c r="F104" s="2"/>
+      <c r="G104" t="s">
+        <v>549</v>
       </c>
       <c r="H104" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="L104" t="s">
         <v>546</v>
       </c>
       <c r="M104" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
-        <v>651041271</v>
+        <v>1214135337</v>
       </c>
       <c r="B105" s="2">
-        <v>863</v>
+        <v>1099</v>
       </c>
       <c r="C105" s="2">
-        <v>3030050188998</v>
+        <v>3030050197594</v>
       </c>
       <c r="D105" t="s">
         <v>910</v>
       </c>
       <c r="E105" t="s">
-        <v>555</v>
-      </c>
-      <c r="F105" s="2"/>
-      <c r="G105" t="s">
-        <v>556</v>
+        <v>552</v>
+      </c>
+      <c r="F105" s="2">
+        <v>995633087</v>
       </c>
       <c r="H105" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="L105" t="s">
         <v>546</v>
       </c>
       <c r="M105" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
-        <v>1214135234</v>
+        <v>651041271</v>
       </c>
       <c r="B106" s="2">
-        <v>1100</v>
+        <v>863</v>
       </c>
       <c r="C106" s="2">
-        <v>3030050197617</v>
+        <v>3030050188998</v>
       </c>
       <c r="D106" t="s">
         <v>910</v>
       </c>
       <c r="E106" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="F106" s="2"/>
+      <c r="G106" t="s">
+        <v>556</v>
+      </c>
       <c r="H106" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="L106" t="s">
         <v>546</v>
       </c>
       <c r="M106" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
-        <v>651275258</v>
+        <v>1214135234</v>
       </c>
       <c r="B107" s="2">
-        <v>864</v>
+        <v>1100</v>
       </c>
       <c r="C107" s="2">
-        <v>3030050188981</v>
+        <v>3030050197617</v>
       </c>
       <c r="D107" t="s">
         <v>910</v>
       </c>
       <c r="E107" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="F107" s="2"/>
       <c r="H107" t="s">
-        <v>563</v>
-      </c>
-      <c r="I107" t="s">
-        <v>564</v>
-      </c>
-      <c r="J107" t="s">
-        <v>565</v>
-      </c>
-      <c r="K107" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="L107" t="s">
         <v>546</v>
       </c>
       <c r="M107" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
-        <v>1501080561</v>
+        <v>651275258</v>
       </c>
       <c r="B108" s="2">
-        <v>1299</v>
+        <v>864</v>
       </c>
       <c r="C108" s="2">
-        <v>3030050197631</v>
+        <v>3030050188981</v>
       </c>
       <c r="D108" t="s">
         <v>910</v>
       </c>
       <c r="E108" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="F108" s="2"/>
       <c r="H108" t="s">
-        <v>569</v>
+        <v>563</v>
+      </c>
+      <c r="I108" t="s">
+        <v>564</v>
+      </c>
+      <c r="J108" t="s">
+        <v>565</v>
+      </c>
+      <c r="K108" t="s">
+        <v>566</v>
       </c>
       <c r="L108" t="s">
         <v>546</v>
       </c>
       <c r="M108" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
-        <v>651041273</v>
+        <v>1501080561</v>
       </c>
       <c r="B109" s="2">
-        <v>865</v>
+        <v>1299</v>
       </c>
       <c r="C109" s="2">
-        <v>3030050188974</v>
+        <v>3030050197631</v>
       </c>
       <c r="D109" t="s">
         <v>910</v>
       </c>
       <c r="E109" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="F109" s="2"/>
       <c r="H109" t="s">
-        <v>572</v>
-      </c>
-      <c r="I109" t="s">
-        <v>573</v>
-      </c>
-      <c r="J109" t="s">
-        <v>574</v>
-      </c>
-      <c r="K109" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="L109" t="s">
         <v>546</v>
       </c>
       <c r="M109" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
-        <v>651040961</v>
+        <v>651041273</v>
       </c>
       <c r="B110" s="2">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C110" s="2">
-        <v>3030050188967</v>
+        <v>3030050188974</v>
       </c>
       <c r="D110" t="s">
         <v>910</v>
       </c>
       <c r="E110" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="F110" s="2"/>
       <c r="H110" t="s">
-        <v>578</v>
+        <v>572</v>
+      </c>
+      <c r="I110" t="s">
+        <v>573</v>
+      </c>
+      <c r="J110" t="s">
+        <v>574</v>
+      </c>
+      <c r="K110" t="s">
+        <v>575</v>
       </c>
       <c r="L110" t="s">
         <v>546</v>
       </c>
       <c r="M110" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
-        <v>1026157257</v>
-      </c>
-      <c r="B111" s="2"/>
+        <v>651040961</v>
+      </c>
+      <c r="B111" s="2">
+        <v>866</v>
+      </c>
       <c r="C111" s="2">
-        <v>761318053309</v>
+        <v>3030050188967</v>
       </c>
       <c r="D111" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="E111" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="F111" s="2"/>
       <c r="H111" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="L111" t="s">
-        <v>515</v>
+        <v>546</v>
       </c>
       <c r="M111" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
-        <v>1961640404</v>
+        <v>1026157257</v>
       </c>
       <c r="B112" s="2"/>
       <c r="C112" s="2">
-        <v>761318952923</v>
+        <v>761318053309</v>
       </c>
       <c r="D112" t="s">
         <v>911</v>
       </c>
       <c r="E112" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="F112" s="2"/>
       <c r="H112" t="s">
-        <v>584</v>
-      </c>
-      <c r="I112" t="s">
-        <v>585</v>
-      </c>
-      <c r="J112" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="L112" t="s">
         <v>515</v>
       </c>
       <c r="M112" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
-        <v>556614684</v>
+        <v>1961640404</v>
       </c>
       <c r="B113" s="2"/>
       <c r="C113" s="2">
-        <v>761318523246</v>
+        <v>761318952923</v>
       </c>
       <c r="D113" t="s">
         <v>911</v>
       </c>
       <c r="E113" t="s">
-        <v>588</v>
-      </c>
-      <c r="F113" s="2">
-        <v>788376581</v>
-      </c>
+        <v>583</v>
+      </c>
+      <c r="F113" s="2"/>
       <c r="H113" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="I113" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="J113" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="L113" t="s">
         <v>515</v>
       </c>
       <c r="M113" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
-        <v>1870944746</v>
+        <v>556614684</v>
       </c>
       <c r="B114" s="2"/>
       <c r="C114" s="2">
-        <v>761318352228</v>
+        <v>761318523246</v>
       </c>
       <c r="D114" t="s">
         <v>911</v>
       </c>
       <c r="E114" t="s">
-        <v>593</v>
-      </c>
-      <c r="F114" s="2"/>
+        <v>588</v>
+      </c>
+      <c r="F114" s="2">
+        <v>788376581</v>
+      </c>
       <c r="H114" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="I114" t="s">
         <v>590</v>
@@ -7077,2390 +7081,2422 @@
       <c r="J114" t="s">
         <v>591</v>
       </c>
-      <c r="K114" t="s">
-        <v>595</v>
-      </c>
       <c r="L114" t="s">
         <v>515</v>
       </c>
       <c r="M114" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
-        <v>305585932</v>
+        <v>1870944746</v>
       </c>
       <c r="B115" s="2"/>
       <c r="C115" s="2">
-        <v>761318553335</v>
+        <v>761318352228</v>
       </c>
       <c r="D115" t="s">
         <v>911</v>
       </c>
       <c r="E115" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="F115" s="2"/>
       <c r="H115" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="I115" t="s">
-        <v>599</v>
+        <v>590</v>
       </c>
       <c r="J115" t="s">
-        <v>600</v>
+        <v>591</v>
       </c>
       <c r="K115" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="L115" t="s">
-        <v>546</v>
+        <v>515</v>
       </c>
       <c r="M115" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
-        <v>27577243</v>
+        <v>305585932</v>
       </c>
       <c r="B116" s="2"/>
       <c r="C116" s="2">
-        <v>761318158233</v>
+        <v>761318553335</v>
       </c>
       <c r="D116" t="s">
         <v>911</v>
       </c>
       <c r="E116" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="F116" s="2"/>
       <c r="H116" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="I116" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="J116" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="K116" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="L116" t="s">
         <v>546</v>
       </c>
       <c r="M116" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
-        <v>1029748986</v>
+        <v>27577243</v>
       </c>
       <c r="B117" s="2"/>
       <c r="C117" s="2">
-        <v>761318653202</v>
+        <v>761318158233</v>
       </c>
       <c r="D117" t="s">
         <v>911</v>
       </c>
       <c r="E117" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="F117" s="2"/>
       <c r="H117" t="s">
-        <v>610</v>
+        <v>604</v>
+      </c>
+      <c r="I117" t="s">
+        <v>605</v>
+      </c>
+      <c r="J117" t="s">
+        <v>606</v>
+      </c>
+      <c r="K117" t="s">
+        <v>607</v>
       </c>
       <c r="L117" t="s">
         <v>546</v>
       </c>
       <c r="M117" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
-        <v>111351299</v>
+        <v>1029748986</v>
       </c>
       <c r="B118" s="2"/>
       <c r="C118" s="2">
-        <v>761318298663</v>
+        <v>761318653202</v>
       </c>
       <c r="D118" t="s">
         <v>911</v>
       </c>
       <c r="E118" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="F118" s="2"/>
-      <c r="G118" t="s">
-        <v>613</v>
-      </c>
       <c r="H118" t="s">
-        <v>614</v>
-      </c>
-      <c r="I118" t="s">
-        <v>615</v>
-      </c>
-      <c r="J118" t="s">
-        <v>616</v>
-      </c>
-      <c r="K118" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="L118" t="s">
-        <v>500</v>
+        <v>546</v>
       </c>
       <c r="M118" t="s">
-        <v>901</v>
+        <v>611</v>
       </c>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
-        <v>305581608</v>
+        <v>111351299</v>
       </c>
       <c r="B119" s="2"/>
       <c r="C119" s="2">
-        <v>761318022114</v>
+        <v>761318298663</v>
       </c>
       <c r="D119" t="s">
         <v>911</v>
       </c>
       <c r="E119" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="F119" s="2"/>
       <c r="G119" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="H119" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="I119" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="J119" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="K119" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="L119" t="s">
         <v>500</v>
       </c>
       <c r="M119" t="s">
-        <v>624</v>
+        <v>901</v>
       </c>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
-        <v>234200534</v>
+        <v>305581608</v>
       </c>
       <c r="B120" s="2"/>
       <c r="C120" s="2">
-        <v>761318621751</v>
+        <v>761318022114</v>
       </c>
       <c r="D120" t="s">
         <v>911</v>
       </c>
       <c r="E120" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="F120" s="2"/>
+      <c r="G120" t="s">
+        <v>619</v>
+      </c>
       <c r="H120" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="I120" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="J120" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="K120" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="L120" t="s">
         <v>500</v>
       </c>
       <c r="M120" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
-        <v>27761983</v>
+        <v>234200534</v>
       </c>
       <c r="B121" s="2"/>
       <c r="C121" s="2">
-        <v>761318452515</v>
+        <v>761318621751</v>
       </c>
       <c r="D121" t="s">
         <v>911</v>
       </c>
       <c r="E121" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="F121" s="2"/>
       <c r="H121" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="I121" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="J121" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="K121" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="L121" t="s">
         <v>500</v>
       </c>
       <c r="M121" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
-        <v>33968912</v>
+        <v>27761983</v>
       </c>
       <c r="B122" s="2"/>
       <c r="C122" s="2">
-        <v>761318252290</v>
+        <v>761318452515</v>
       </c>
       <c r="D122" t="s">
         <v>911</v>
       </c>
       <c r="E122" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="F122" s="2"/>
       <c r="H122" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="I122" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="J122" t="s">
-        <v>640</v>
+        <v>634</v>
+      </c>
+      <c r="K122" t="s">
+        <v>635</v>
       </c>
       <c r="L122" t="s">
         <v>500</v>
       </c>
       <c r="M122" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
-        <v>234200782</v>
+        <v>33968912</v>
       </c>
       <c r="B123" s="2"/>
       <c r="C123" s="2">
-        <v>761318053057</v>
+        <v>761318252290</v>
       </c>
       <c r="D123" t="s">
         <v>911</v>
       </c>
       <c r="E123" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="F123" s="2"/>
       <c r="H123" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="I123" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="J123" t="s">
-        <v>645</v>
-      </c>
-      <c r="K123" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="L123" t="s">
         <v>500</v>
       </c>
       <c r="M123" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
-        <v>812077192</v>
+        <v>234200782</v>
       </c>
       <c r="B124" s="2"/>
       <c r="C124" s="2">
-        <v>761318253358</v>
+        <v>761318053057</v>
       </c>
       <c r="D124" t="s">
         <v>911</v>
       </c>
       <c r="E124" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="F124" s="2"/>
       <c r="H124" t="s">
-        <v>649</v>
+        <v>643</v>
+      </c>
+      <c r="I124" t="s">
+        <v>644</v>
+      </c>
+      <c r="J124" t="s">
+        <v>645</v>
+      </c>
+      <c r="K124" t="s">
+        <v>646</v>
       </c>
       <c r="L124" t="s">
-        <v>650</v>
+        <v>500</v>
       </c>
       <c r="M124" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
-        <v>1091269927</v>
+        <v>812077192</v>
       </c>
       <c r="B125" s="2"/>
       <c r="C125" s="2">
-        <v>761318253266</v>
+        <v>761318253358</v>
       </c>
       <c r="D125" t="s">
         <v>911</v>
       </c>
       <c r="E125" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="F125" s="2"/>
       <c r="H125" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="L125" t="s">
         <v>650</v>
       </c>
       <c r="M125" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
-        <v>909963089</v>
+        <v>1091269927</v>
       </c>
       <c r="B126" s="2"/>
       <c r="C126" s="2">
-        <v>761318253259</v>
+        <v>761318253266</v>
       </c>
       <c r="D126" t="s">
         <v>911</v>
       </c>
       <c r="E126" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="F126" s="2"/>
       <c r="H126" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="L126" t="s">
         <v>650</v>
       </c>
       <c r="M126" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
-        <v>1274726842</v>
-      </c>
-      <c r="B127" s="2">
-        <v>1113</v>
-      </c>
+        <v>909963089</v>
+      </c>
+      <c r="B127" s="2"/>
       <c r="C127" s="2">
-        <v>8006530054102</v>
+        <v>761318253259</v>
       </c>
       <c r="D127" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="E127" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="F127" s="2"/>
-      <c r="I127" t="s">
-        <v>659</v>
-      </c>
-      <c r="K127" t="s">
-        <v>660</v>
+      <c r="H127" t="s">
+        <v>656</v>
       </c>
       <c r="L127" t="s">
-        <v>661</v>
+        <v>650</v>
       </c>
       <c r="M127" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
-        <v>310098109</v>
+        <v>1274726842</v>
       </c>
       <c r="B128" s="2">
-        <v>782</v>
+        <v>1113</v>
       </c>
       <c r="C128" s="2">
-        <v>4210201434658</v>
+        <v>8006530054102</v>
       </c>
       <c r="D128" t="s">
         <v>912</v>
       </c>
       <c r="E128" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="F128" s="2"/>
       <c r="I128" t="s">
-        <v>664</v>
-      </c>
-      <c r="J128" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="K128" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="L128" t="s">
         <v>661</v>
       </c>
       <c r="M128" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
-        <v>860883903</v>
+        <v>310098109</v>
       </c>
       <c r="B129" s="2">
-        <v>622</v>
+        <v>782</v>
       </c>
       <c r="C129" s="2">
-        <v>4210201439868</v>
+        <v>4210201434658</v>
       </c>
       <c r="D129" t="s">
         <v>912</v>
       </c>
       <c r="E129" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="F129" s="2"/>
       <c r="I129" t="s">
-        <v>669</v>
+        <v>664</v>
+      </c>
+      <c r="J129" t="s">
+        <v>665</v>
       </c>
       <c r="K129" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="L129" t="s">
         <v>661</v>
       </c>
       <c r="M129" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
     </row>
     <row r="130" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
-        <v>1654361123</v>
+        <v>860883903</v>
       </c>
       <c r="B130" s="2">
-        <v>1276</v>
+        <v>622</v>
       </c>
       <c r="C130" s="2">
-        <v>4210201411512</v>
+        <v>4210201439868</v>
       </c>
       <c r="D130" t="s">
         <v>912</v>
       </c>
       <c r="E130" t="s">
-        <v>915</v>
+        <v>668</v>
+      </c>
+      <c r="F130" s="2"/>
+      <c r="I130" t="s">
+        <v>669</v>
+      </c>
+      <c r="K130" t="s">
+        <v>670</v>
       </c>
       <c r="L130" t="s">
         <v>661</v>
       </c>
       <c r="M130" t="s">
-        <v>918</v>
+        <v>671</v>
       </c>
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
-        <v>1573231488</v>
+        <v>1654361123</v>
       </c>
       <c r="B131" s="2">
-        <v>469</v>
+        <v>1276</v>
       </c>
       <c r="C131" s="2">
-        <v>4210201303015</v>
+        <v>4210201411512</v>
       </c>
       <c r="D131" t="s">
         <v>912</v>
       </c>
       <c r="E131" t="s">
-        <v>672</v>
-      </c>
-      <c r="F131" s="2"/>
-      <c r="I131" t="s">
-        <v>673</v>
-      </c>
-      <c r="J131" t="s">
-        <v>674</v>
-      </c>
-      <c r="K131" t="s">
-        <v>675</v>
+        <v>915</v>
       </c>
       <c r="L131" t="s">
         <v>661</v>
       </c>
       <c r="M131" t="s">
-        <v>676</v>
+        <v>918</v>
       </c>
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
-        <v>1968311343</v>
+        <v>1573231488</v>
       </c>
       <c r="B132" s="2">
-        <v>804</v>
+        <v>469</v>
       </c>
       <c r="C132" s="2">
-        <v>4210201408390</v>
+        <v>4210201303015</v>
       </c>
       <c r="D132" t="s">
         <v>912</v>
       </c>
       <c r="E132" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="F132" s="2"/>
       <c r="I132" t="s">
-        <v>678</v>
+        <v>673</v>
+      </c>
+      <c r="J132" t="s">
+        <v>674</v>
       </c>
       <c r="K132" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="L132" t="s">
         <v>661</v>
       </c>
       <c r="M132" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
-        <v>1573231610</v>
-      </c>
-      <c r="B133" s="2"/>
+        <v>1968311343</v>
+      </c>
+      <c r="B133" s="2">
+        <v>804</v>
+      </c>
       <c r="C133" s="2">
-        <v>4210201362869</v>
+        <v>4210201408390</v>
       </c>
       <c r="D133" t="s">
         <v>912</v>
       </c>
       <c r="E133" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="F133" s="2"/>
+      <c r="I133" t="s">
+        <v>678</v>
+      </c>
+      <c r="K133" t="s">
+        <v>679</v>
+      </c>
       <c r="L133" t="s">
         <v>661</v>
       </c>
       <c r="M133" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
-        <v>1619570919</v>
-      </c>
-      <c r="B134" s="2">
-        <v>1297</v>
-      </c>
+        <v>1573231610</v>
+      </c>
+      <c r="B134" s="2"/>
       <c r="C134" s="2">
-        <v>4210201445111</v>
+        <v>4210201362869</v>
       </c>
       <c r="D134" t="s">
         <v>912</v>
       </c>
       <c r="E134" t="s">
-        <v>916</v>
+        <v>681</v>
       </c>
       <c r="F134" s="2"/>
       <c r="L134" t="s">
         <v>661</v>
       </c>
       <c r="M134" t="s">
-        <v>923</v>
+        <v>682</v>
       </c>
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
-        <v>925198561</v>
+        <v>1619570919</v>
       </c>
       <c r="B135" s="2">
-        <v>1017</v>
+        <v>1297</v>
       </c>
       <c r="C135" s="2">
-        <v>4210201437857</v>
+        <v>4210201445111</v>
       </c>
       <c r="D135" t="s">
         <v>912</v>
       </c>
       <c r="E135" t="s">
-        <v>683</v>
+        <v>916</v>
       </c>
       <c r="F135" s="2"/>
-      <c r="I135" t="s">
-        <v>684</v>
-      </c>
-      <c r="J135" t="s">
-        <v>685</v>
-      </c>
-      <c r="K135" t="s">
-        <v>686</v>
-      </c>
       <c r="L135" t="s">
         <v>661</v>
       </c>
       <c r="M135" t="s">
-        <v>687</v>
+        <v>923</v>
       </c>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
-        <v>1573231438</v>
+        <v>925198561</v>
       </c>
       <c r="B136" s="2">
-        <v>460</v>
+        <v>1017</v>
       </c>
       <c r="C136" s="2">
-        <v>4210201381648</v>
+        <v>4210201437857</v>
       </c>
       <c r="D136" t="s">
         <v>912</v>
       </c>
       <c r="E136" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="F136" s="2"/>
+      <c r="I136" t="s">
+        <v>684</v>
+      </c>
+      <c r="J136" t="s">
+        <v>685</v>
+      </c>
+      <c r="K136" t="s">
+        <v>686</v>
+      </c>
       <c r="L136" t="s">
         <v>661</v>
       </c>
       <c r="M136" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
-        <v>2017920996</v>
+        <v>1573231438</v>
       </c>
       <c r="B137" s="2">
-        <v>579</v>
+        <v>460</v>
       </c>
       <c r="C137" s="2">
-        <v>4210201415534</v>
+        <v>4210201381648</v>
       </c>
       <c r="D137" t="s">
         <v>912</v>
       </c>
       <c r="E137" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="F137" s="2"/>
       <c r="L137" t="s">
         <v>661</v>
       </c>
       <c r="M137" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
     </row>
     <row r="138" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
-        <v>2083605028</v>
+        <v>2017920996</v>
       </c>
       <c r="B138" s="2">
-        <v>621</v>
+        <v>579</v>
       </c>
       <c r="C138" s="2">
-        <v>4210201415558</v>
+        <v>4210201415534</v>
       </c>
       <c r="D138" t="s">
         <v>912</v>
       </c>
       <c r="E138" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="F138" s="2"/>
-      <c r="I138" t="s">
-        <v>693</v>
-      </c>
-      <c r="K138" t="s">
-        <v>694</v>
-      </c>
       <c r="L138" t="s">
         <v>661</v>
       </c>
       <c r="M138" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
-        <v>232581281</v>
+        <v>2083605028</v>
       </c>
       <c r="B139" s="2">
-        <v>746</v>
+        <v>621</v>
       </c>
       <c r="C139" s="2">
-        <v>8006540731178</v>
+        <v>4210201415558</v>
       </c>
       <c r="D139" t="s">
         <v>912</v>
       </c>
       <c r="E139" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="F139" s="2"/>
       <c r="I139" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="K139" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="L139" t="s">
         <v>661</v>
       </c>
       <c r="M139" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
-        <v>268085864</v>
+        <v>232581281</v>
       </c>
       <c r="B140" s="2">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C140" s="2">
-        <v>8006540731185</v>
+        <v>8006540731178</v>
       </c>
       <c r="D140" t="s">
         <v>912</v>
       </c>
       <c r="E140" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="F140" s="2"/>
       <c r="I140" t="s">
-        <v>701</v>
+        <v>697</v>
+      </c>
+      <c r="K140" t="s">
+        <v>698</v>
       </c>
       <c r="L140" t="s">
         <v>661</v>
       </c>
       <c r="M140" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
-        <v>232560211</v>
+        <v>268085864</v>
       </c>
       <c r="B141" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="C141" s="2">
-        <v>8006540731154</v>
+        <v>8006540731185</v>
       </c>
       <c r="D141" t="s">
         <v>912</v>
       </c>
       <c r="E141" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="F141" s="2"/>
       <c r="I141" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="L141" t="s">
         <v>661</v>
       </c>
       <c r="M141" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
     </row>
     <row r="142" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A142" s="2">
-        <v>1610045907</v>
+        <v>232560211</v>
       </c>
       <c r="B142" s="2">
-        <v>1279</v>
+        <v>745</v>
       </c>
       <c r="C142" s="2">
-        <v>8006530069229</v>
+        <v>8006540731154</v>
       </c>
       <c r="D142" t="s">
         <v>912</v>
       </c>
       <c r="E142" t="s">
-        <v>920</v>
+        <v>703</v>
       </c>
       <c r="F142" s="2"/>
+      <c r="I142" t="s">
+        <v>704</v>
+      </c>
       <c r="L142" t="s">
         <v>661</v>
       </c>
       <c r="M142" t="s">
-        <v>921</v>
+        <v>705</v>
       </c>
     </row>
     <row r="143" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
-        <v>968556310</v>
+        <v>1610045907</v>
       </c>
       <c r="B143" s="2">
-        <v>1110</v>
+        <v>1279</v>
       </c>
       <c r="C143" s="2">
-        <v>8700216368568</v>
+        <v>8006530069229</v>
       </c>
       <c r="D143" t="s">
         <v>912</v>
       </c>
       <c r="E143" t="s">
-        <v>706</v>
+        <v>920</v>
       </c>
       <c r="F143" s="2"/>
-      <c r="I143" t="s">
-        <v>707</v>
-      </c>
-      <c r="J143" t="s">
-        <v>708</v>
-      </c>
-      <c r="K143" t="s">
-        <v>709</v>
-      </c>
       <c r="L143" t="s">
         <v>661</v>
       </c>
       <c r="M143" t="s">
-        <v>710</v>
+        <v>921</v>
       </c>
     </row>
     <row r="144" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
-        <v>969060801</v>
+        <v>968556310</v>
       </c>
       <c r="B144" s="2">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="C144" s="2">
-        <v>8700216344784</v>
+        <v>8700216368568</v>
       </c>
       <c r="D144" t="s">
         <v>912</v>
       </c>
       <c r="E144" t="s">
-        <v>711</v>
+        <v>706</v>
       </c>
       <c r="F144" s="2"/>
       <c r="I144" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="J144" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
       <c r="K144" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="L144" t="s">
         <v>661</v>
       </c>
       <c r="M144" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
     </row>
     <row r="145" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
-        <v>968672789</v>
+        <v>969060801</v>
       </c>
       <c r="B145" s="2">
-        <v>1023</v>
+        <v>1108</v>
       </c>
       <c r="C145" s="2">
-        <v>8700216523202</v>
+        <v>8700216344784</v>
       </c>
       <c r="D145" t="s">
         <v>912</v>
       </c>
       <c r="E145" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
       <c r="F145" s="2"/>
       <c r="I145" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="J145" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="K145" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="L145" t="s">
         <v>661</v>
       </c>
       <c r="M145" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
     </row>
     <row r="146" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
-        <v>1259500517</v>
+        <v>968672789</v>
       </c>
       <c r="B146" s="2">
-        <v>1112</v>
+        <v>1023</v>
       </c>
       <c r="C146" s="2">
-        <v>8700216932479</v>
+        <v>8700216523202</v>
       </c>
       <c r="D146" t="s">
         <v>912</v>
       </c>
       <c r="E146" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="F146" s="2"/>
       <c r="I146" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="J146" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="K146" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="L146" t="s">
         <v>661</v>
       </c>
       <c r="M146" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
     </row>
     <row r="147" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A147" s="2">
-        <v>1474948616</v>
+        <v>1259500517</v>
       </c>
       <c r="B147" s="2">
-        <v>1300</v>
+        <v>1112</v>
       </c>
       <c r="C147" s="2">
-        <v>8700216932370</v>
+        <v>8700216932479</v>
       </c>
       <c r="D147" t="s">
         <v>912</v>
       </c>
       <c r="E147" t="s">
-        <v>917</v>
+        <v>721</v>
       </c>
       <c r="F147" s="2"/>
+      <c r="I147" t="s">
+        <v>722</v>
+      </c>
+      <c r="J147" t="s">
+        <v>723</v>
+      </c>
+      <c r="K147" t="s">
+        <v>724</v>
+      </c>
       <c r="L147" t="s">
         <v>661</v>
       </c>
       <c r="M147" t="s">
-        <v>919</v>
+        <v>725</v>
       </c>
     </row>
     <row r="148" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A148" s="2">
-        <v>968672794</v>
+        <v>1474948616</v>
       </c>
       <c r="B148" s="2">
-        <v>1020</v>
+        <v>1300</v>
       </c>
       <c r="C148" s="2">
-        <v>8700216344586</v>
+        <v>8700216932370</v>
       </c>
       <c r="D148" t="s">
         <v>912</v>
       </c>
       <c r="E148" t="s">
-        <v>726</v>
+        <v>917</v>
       </c>
       <c r="F148" s="2"/>
       <c r="L148" t="s">
         <v>661</v>
       </c>
       <c r="M148" t="s">
-        <v>727</v>
+        <v>919</v>
       </c>
     </row>
     <row r="149" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
-        <v>968672793</v>
+        <v>968672794</v>
       </c>
       <c r="B149" s="2">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="C149" s="2">
-        <v>8700216523233</v>
+        <v>8700216344586</v>
       </c>
       <c r="D149" t="s">
         <v>912</v>
       </c>
       <c r="E149" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="F149" s="2"/>
       <c r="L149" t="s">
         <v>661</v>
       </c>
       <c r="M149" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
     </row>
     <row r="150" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
-        <v>1376163630</v>
-      </c>
-      <c r="B150" s="2"/>
+        <v>968672793</v>
+      </c>
+      <c r="B150" s="2">
+        <v>1021</v>
+      </c>
       <c r="C150" s="2">
-        <v>4210201397007</v>
+        <v>8700216523233</v>
       </c>
       <c r="D150" t="s">
         <v>912</v>
       </c>
       <c r="E150" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="F150" s="2"/>
       <c r="L150" t="s">
         <v>661</v>
       </c>
       <c r="M150" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
     </row>
     <row r="151" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
-        <v>540380502</v>
-      </c>
-      <c r="B151" s="2">
-        <v>484</v>
-      </c>
+        <v>1376163630</v>
+      </c>
+      <c r="B151" s="2"/>
       <c r="C151" s="2">
-        <v>4210201238515</v>
+        <v>4210201397007</v>
       </c>
       <c r="D151" t="s">
         <v>912</v>
       </c>
       <c r="E151" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="F151" s="2"/>
       <c r="L151" t="s">
         <v>661</v>
       </c>
       <c r="M151" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
     </row>
     <row r="152" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
-        <v>1370306528</v>
+        <v>540380502</v>
       </c>
       <c r="B152" s="2">
-        <v>809</v>
+        <v>484</v>
       </c>
       <c r="C152" s="2">
-        <v>4210201395492</v>
+        <v>4210201238515</v>
       </c>
       <c r="D152" t="s">
         <v>912</v>
       </c>
       <c r="E152" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="F152" s="2"/>
       <c r="L152" t="s">
         <v>661</v>
       </c>
       <c r="M152" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
     </row>
     <row r="153" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
-        <v>354067553</v>
+        <v>1370306528</v>
       </c>
       <c r="B153" s="2">
-        <v>1121</v>
+        <v>809</v>
       </c>
       <c r="C153" s="2">
-        <v>8001090915061</v>
+        <v>4210201395492</v>
       </c>
       <c r="D153" t="s">
         <v>912</v>
       </c>
       <c r="E153" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="F153" s="2"/>
-      <c r="I153" t="s">
-        <v>737</v>
-      </c>
-      <c r="J153" t="s">
-        <v>738</v>
-      </c>
-      <c r="K153" t="s">
-        <v>739</v>
-      </c>
       <c r="L153" t="s">
         <v>661</v>
       </c>
       <c r="M153" t="s">
-        <v>740</v>
+        <v>735</v>
       </c>
     </row>
     <row r="154" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
-        <v>737753404</v>
+        <v>354067553</v>
       </c>
       <c r="B154" s="2">
-        <v>752</v>
+        <v>1121</v>
       </c>
       <c r="C154" s="2">
-        <v>8001090919038</v>
+        <v>8001090915061</v>
       </c>
       <c r="D154" t="s">
         <v>912</v>
       </c>
       <c r="E154" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="F154" s="2"/>
       <c r="I154" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="J154" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="K154" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="L154" t="s">
         <v>661</v>
       </c>
       <c r="M154" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
     </row>
     <row r="155" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A155" s="2">
-        <v>737753400</v>
+        <v>737753404</v>
       </c>
       <c r="B155" s="2">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="C155" s="2">
-        <v>8001090916372</v>
+        <v>8001090919038</v>
       </c>
       <c r="D155" t="s">
         <v>912</v>
       </c>
       <c r="E155" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
       <c r="F155" s="2"/>
       <c r="I155" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="J155" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="K155" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="L155" t="s">
         <v>661</v>
       </c>
       <c r="M155" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
     </row>
     <row r="156" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A156" s="2">
-        <v>323720959</v>
+        <v>737753400</v>
       </c>
       <c r="B156" s="2">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="C156" s="2">
-        <v>8006540841549</v>
+        <v>8001090916372</v>
       </c>
       <c r="D156" t="s">
         <v>912</v>
       </c>
       <c r="E156" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="F156" s="2"/>
       <c r="I156" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="J156" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="K156" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
       <c r="L156" t="s">
         <v>661</v>
       </c>
       <c r="M156" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
     </row>
     <row r="157" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
-        <v>721123482</v>
+        <v>323720959</v>
       </c>
       <c r="B157" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="C157" s="2">
-        <v>8006540839744</v>
+        <v>8006540841549</v>
       </c>
       <c r="D157" t="s">
         <v>912</v>
       </c>
       <c r="E157" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="F157" s="2"/>
       <c r="I157" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="J157" t="s">
-        <v>758</v>
+        <v>753</v>
       </c>
       <c r="K157" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="L157" t="s">
         <v>661</v>
       </c>
       <c r="M157" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
     </row>
     <row r="158" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
-        <v>425126</v>
-      </c>
-      <c r="B158" s="2"/>
+        <v>721123482</v>
+      </c>
+      <c r="B158" s="2">
+        <v>742</v>
+      </c>
       <c r="C158" s="2">
-        <v>4210201378617</v>
+        <v>8006540839744</v>
       </c>
       <c r="D158" t="s">
         <v>912</v>
       </c>
       <c r="E158" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="F158" s="2"/>
+      <c r="I158" t="s">
+        <v>757</v>
+      </c>
+      <c r="J158" t="s">
+        <v>758</v>
+      </c>
+      <c r="K158" t="s">
+        <v>759</v>
+      </c>
       <c r="L158" t="s">
         <v>661</v>
       </c>
       <c r="M158" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="159" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A159" s="2">
-        <v>327888805</v>
-      </c>
-      <c r="B159" s="2">
-        <v>1006</v>
-      </c>
+        <v>425126</v>
+      </c>
+      <c r="B159" s="2"/>
       <c r="C159" s="2">
-        <v>8006540772515</v>
+        <v>4210201378617</v>
       </c>
       <c r="D159" t="s">
         <v>912</v>
       </c>
       <c r="E159" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="F159" s="2"/>
-      <c r="I159" t="s">
-        <v>764</v>
-      </c>
-      <c r="J159" t="s">
-        <v>765</v>
-      </c>
-      <c r="K159" t="s">
-        <v>766</v>
-      </c>
       <c r="L159" t="s">
         <v>661</v>
       </c>
       <c r="M159" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
     </row>
     <row r="160" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A160" s="2">
-        <v>372814572</v>
+        <v>327888805</v>
       </c>
       <c r="B160" s="2">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C160" s="2">
-        <v>8006540772812</v>
+        <v>8006540772515</v>
       </c>
       <c r="D160" t="s">
         <v>912</v>
       </c>
       <c r="E160" t="s">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="F160" s="2"/>
       <c r="I160" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="J160" t="s">
-        <v>770</v>
+        <v>765</v>
       </c>
       <c r="K160" t="s">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="L160" t="s">
         <v>661</v>
       </c>
       <c r="M160" t="s">
-        <v>772</v>
+        <v>767</v>
       </c>
     </row>
     <row r="161" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A161" s="2">
-        <v>769804933</v>
+        <v>372814572</v>
       </c>
       <c r="B161" s="2">
-        <v>947</v>
+        <v>1005</v>
       </c>
       <c r="C161" s="2">
-        <v>8700216297172</v>
+        <v>8006540772812</v>
       </c>
       <c r="D161" t="s">
         <v>912</v>
       </c>
       <c r="E161" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="F161" s="2"/>
       <c r="I161" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="J161" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="K161" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="L161" t="s">
         <v>661</v>
       </c>
       <c r="M161" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
     </row>
     <row r="162" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A162" s="2">
-        <v>2029028576</v>
+        <v>769804933</v>
       </c>
       <c r="B162" s="2">
-        <v>1127</v>
+        <v>947</v>
       </c>
       <c r="C162" s="2">
-        <v>4210201427087</v>
+        <v>8700216297172</v>
       </c>
       <c r="D162" t="s">
         <v>912</v>
       </c>
       <c r="E162" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="F162" s="2"/>
       <c r="I162" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="J162" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
       <c r="K162" t="s">
-        <v>781</v>
+        <v>776</v>
       </c>
       <c r="L162" t="s">
         <v>661</v>
       </c>
       <c r="M162" t="s">
-        <v>782</v>
+        <v>777</v>
       </c>
     </row>
     <row r="163" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
-        <v>2032683293</v>
+        <v>2029028576</v>
       </c>
       <c r="B163" s="2">
-        <v>591</v>
+        <v>1127</v>
       </c>
       <c r="C163" s="2">
-        <v>4210201434597</v>
+        <v>4210201427087</v>
       </c>
       <c r="D163" t="s">
         <v>912</v>
       </c>
       <c r="E163" t="s">
-        <v>783</v>
+        <v>778</v>
       </c>
       <c r="F163" s="2"/>
+      <c r="I163" t="s">
+        <v>779</v>
+      </c>
+      <c r="J163" t="s">
+        <v>780</v>
+      </c>
+      <c r="K163" t="s">
+        <v>781</v>
+      </c>
       <c r="L163" t="s">
         <v>661</v>
       </c>
       <c r="M163" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="164" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A164" s="2">
-        <v>2032715365</v>
-      </c>
-      <c r="B164" s="2"/>
+        <v>2032683293</v>
+      </c>
+      <c r="B164" s="2">
+        <v>591</v>
+      </c>
       <c r="C164" s="2">
-        <v>4210201419723</v>
+        <v>4210201434597</v>
       </c>
       <c r="D164" t="s">
         <v>912</v>
       </c>
       <c r="E164" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="F164" s="2"/>
       <c r="L164" t="s">
         <v>661</v>
       </c>
       <c r="M164" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="165" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A165" s="2">
-        <v>534608159</v>
-      </c>
-      <c r="B165" s="2">
-        <v>919</v>
-      </c>
+        <v>2032715365</v>
+      </c>
+      <c r="B165" s="2"/>
       <c r="C165" s="2">
-        <v>4210201383147</v>
+        <v>4210201419723</v>
       </c>
       <c r="D165" t="s">
         <v>912</v>
       </c>
       <c r="E165" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="F165" s="2"/>
       <c r="L165" t="s">
         <v>661</v>
       </c>
       <c r="M165" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="166" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A166" s="2">
-        <v>380572636</v>
-      </c>
-      <c r="B166" s="2"/>
+        <v>534608159</v>
+      </c>
+      <c r="B166" s="2">
+        <v>919</v>
+      </c>
       <c r="C166" s="2">
-        <v>4210201428749</v>
+        <v>4210201383147</v>
       </c>
       <c r="D166" t="s">
         <v>912</v>
       </c>
       <c r="E166" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="F166" s="2"/>
-      <c r="I166" t="s">
-        <v>790</v>
-      </c>
       <c r="L166" t="s">
-        <v>791</v>
+        <v>661</v>
       </c>
       <c r="M166" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
     </row>
     <row r="167" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A167" s="2">
-        <v>1585101758</v>
-      </c>
-      <c r="B167" s="2">
-        <v>467</v>
-      </c>
+        <v>380572636</v>
+      </c>
+      <c r="B167" s="2"/>
       <c r="C167" s="2">
-        <v>4210201343684</v>
+        <v>4210201428749</v>
       </c>
       <c r="D167" t="s">
         <v>912</v>
       </c>
       <c r="E167" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="F167" s="2"/>
       <c r="I167" t="s">
-        <v>794</v>
-      </c>
-      <c r="J167" t="s">
-        <v>795</v>
-      </c>
-      <c r="K167" t="s">
-        <v>796</v>
+        <v>790</v>
       </c>
       <c r="L167" t="s">
         <v>791</v>
       </c>
       <c r="M167" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
     </row>
     <row r="168" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A168" s="2">
-        <v>1572075225</v>
+        <v>1585101758</v>
       </c>
       <c r="B168" s="2">
-        <v>1038</v>
+        <v>467</v>
       </c>
       <c r="C168" s="2">
-        <v>8700216604932</v>
+        <v>4210201343684</v>
       </c>
       <c r="D168" t="s">
         <v>912</v>
       </c>
       <c r="E168" t="s">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="F168" s="2"/>
       <c r="I168" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="J168" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="K168" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
       <c r="L168" t="s">
         <v>791</v>
       </c>
       <c r="M168" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
     </row>
     <row r="169" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A169" s="2">
-        <v>2031152536</v>
+        <v>1572075225</v>
       </c>
       <c r="B169" s="2">
-        <v>1032</v>
+        <v>1038</v>
       </c>
       <c r="C169" s="2">
-        <v>4210201436829</v>
+        <v>8700216604932</v>
       </c>
       <c r="D169" t="s">
         <v>912</v>
       </c>
       <c r="E169" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="F169" s="2"/>
       <c r="I169" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="J169" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="K169" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="L169" t="s">
         <v>791</v>
       </c>
       <c r="M169" t="s">
-        <v>902</v>
+        <v>802</v>
       </c>
     </row>
     <row r="170" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A170" s="2">
-        <v>1259500163</v>
+        <v>2031152536</v>
       </c>
       <c r="B170" s="2">
-        <v>1111</v>
+        <v>1032</v>
       </c>
       <c r="C170" s="2">
-        <v>8700216930710</v>
+        <v>4210201436829</v>
       </c>
       <c r="D170" t="s">
         <v>912</v>
       </c>
       <c r="E170" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="F170" s="2"/>
       <c r="I170" t="s">
-        <v>808</v>
+        <v>804</v>
+      </c>
+      <c r="J170" t="s">
+        <v>805</v>
       </c>
       <c r="K170" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="L170" t="s">
         <v>791</v>
       </c>
       <c r="M170" t="s">
-        <v>810</v>
+        <v>902</v>
       </c>
     </row>
     <row r="171" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A171" s="2">
-        <v>860325518</v>
+        <v>1259500163</v>
       </c>
       <c r="B171" s="2">
-        <v>1035</v>
+        <v>1111</v>
       </c>
       <c r="C171" s="2">
-        <v>4210201342502</v>
+        <v>8700216930710</v>
       </c>
       <c r="D171" t="s">
         <v>912</v>
       </c>
       <c r="E171" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="F171" s="2"/>
       <c r="I171" t="s">
-        <v>812</v>
-      </c>
-      <c r="J171" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="K171" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="L171" t="s">
         <v>791</v>
       </c>
       <c r="M171" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
     </row>
     <row r="172" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A172" s="2">
-        <v>1573231688</v>
+        <v>860325518</v>
       </c>
       <c r="B172" s="2">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="C172" s="2">
-        <v>4210201342489</v>
+        <v>4210201342502</v>
       </c>
       <c r="D172" t="s">
         <v>912</v>
       </c>
       <c r="E172" t="s">
-        <v>816</v>
+        <v>811</v>
       </c>
       <c r="F172" s="2"/>
       <c r="I172" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
       <c r="J172" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="K172" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="L172" t="s">
         <v>791</v>
       </c>
       <c r="M172" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
     </row>
     <row r="173" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A173" s="2">
-        <v>1585101759</v>
+        <v>1573231688</v>
       </c>
       <c r="B173" s="2">
-        <v>468</v>
+        <v>1034</v>
       </c>
       <c r="C173" s="2">
-        <v>4210201343646</v>
+        <v>4210201342489</v>
       </c>
       <c r="D173" t="s">
         <v>912</v>
       </c>
       <c r="E173" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
       <c r="F173" s="2"/>
       <c r="I173" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="J173" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="K173" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="L173" t="s">
         <v>791</v>
       </c>
       <c r="M173" t="s">
-        <v>903</v>
+        <v>820</v>
       </c>
     </row>
     <row r="174" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A174" s="2">
-        <v>2031152682</v>
+        <v>1585101759</v>
       </c>
       <c r="B174" s="2">
-        <v>604</v>
+        <v>468</v>
       </c>
       <c r="C174" s="2">
-        <v>4210201436843</v>
+        <v>4210201343646</v>
       </c>
       <c r="D174" t="s">
         <v>912</v>
       </c>
       <c r="E174" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="F174" s="2"/>
       <c r="I174" t="s">
-        <v>826</v>
+        <v>822</v>
+      </c>
+      <c r="J174" t="s">
+        <v>823</v>
+      </c>
+      <c r="K174" t="s">
+        <v>824</v>
       </c>
       <c r="L174" t="s">
         <v>791</v>
       </c>
       <c r="M174" t="s">
-        <v>827</v>
+        <v>903</v>
       </c>
     </row>
     <row r="175" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A175" s="2">
-        <v>384637730</v>
+        <v>2031152682</v>
       </c>
       <c r="B175" s="2">
-        <v>803</v>
+        <v>604</v>
       </c>
       <c r="C175" s="2">
-        <v>8700216018913</v>
+        <v>4210201436843</v>
       </c>
       <c r="D175" t="s">
         <v>912</v>
       </c>
       <c r="E175" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="F175" s="2"/>
       <c r="I175" t="s">
-        <v>829</v>
-      </c>
-      <c r="J175" t="s">
-        <v>830</v>
-      </c>
-      <c r="K175" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="L175" t="s">
         <v>791</v>
       </c>
       <c r="M175" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="176" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A176" s="2">
-        <v>1559764588</v>
+        <v>384637730</v>
       </c>
       <c r="B176" s="2">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="C176" s="2">
-        <v>8700216018968</v>
+        <v>8700216018913</v>
       </c>
       <c r="D176" t="s">
         <v>912</v>
       </c>
       <c r="E176" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="F176" s="2"/>
       <c r="I176" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="J176" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="K176" t="s">
-        <v>836</v>
+        <v>831</v>
       </c>
       <c r="L176" t="s">
         <v>791</v>
       </c>
       <c r="M176" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
     </row>
     <row r="177" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A177" s="2">
-        <v>546381109</v>
+        <v>1559764588</v>
       </c>
       <c r="B177" s="2">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="C177" s="2">
-        <v>8700216018845</v>
+        <v>8700216018968</v>
       </c>
       <c r="D177" t="s">
         <v>912</v>
       </c>
       <c r="E177" t="s">
-        <v>838</v>
+        <v>833</v>
       </c>
       <c r="F177" s="2"/>
       <c r="I177" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="J177" t="s">
-        <v>840</v>
+        <v>835</v>
+      </c>
+      <c r="K177" t="s">
+        <v>836</v>
       </c>
       <c r="L177" t="s">
         <v>791</v>
       </c>
       <c r="M177" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
     </row>
     <row r="178" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A178" s="2">
-        <v>1559764588</v>
-      </c>
-      <c r="B178" s="2"/>
+        <v>546381109</v>
+      </c>
+      <c r="B178" s="2">
+        <v>802</v>
+      </c>
       <c r="C178" s="2">
-        <v>4210201321477</v>
+        <v>8700216018845</v>
       </c>
       <c r="D178" t="s">
         <v>912</v>
       </c>
       <c r="E178" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="F178" s="2"/>
       <c r="I178" t="s">
-        <v>843</v>
+        <v>839</v>
+      </c>
+      <c r="J178" t="s">
+        <v>840</v>
       </c>
       <c r="L178" t="s">
         <v>791</v>
       </c>
       <c r="M178" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
     </row>
     <row r="179" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A179" s="2">
-        <v>5982884</v>
+        <v>1559764588</v>
       </c>
       <c r="B179" s="2"/>
       <c r="C179" s="2">
-        <v>4210201321071</v>
+        <v>4210201321477</v>
       </c>
       <c r="D179" t="s">
         <v>912</v>
       </c>
       <c r="E179" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="F179" s="2"/>
       <c r="I179" t="s">
-        <v>845</v>
-      </c>
-      <c r="K179" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="L179" t="s">
         <v>791</v>
       </c>
       <c r="M179" t="s">
-        <v>847</v>
+        <v>837</v>
       </c>
     </row>
     <row r="180" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A180" s="2">
-        <v>620225240</v>
-      </c>
-      <c r="B180" s="2">
-        <v>829</v>
-      </c>
+        <v>5982884</v>
+      </c>
+      <c r="B180" s="2"/>
       <c r="C180" s="2">
-        <v>8006540846186</v>
+        <v>4210201321071</v>
       </c>
       <c r="D180" t="s">
         <v>912</v>
       </c>
       <c r="E180" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="F180" s="2"/>
       <c r="I180" t="s">
-        <v>849</v>
-      </c>
-      <c r="J180" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="K180" t="s">
-        <v>851</v>
+        <v>846</v>
       </c>
       <c r="L180" t="s">
         <v>791</v>
       </c>
       <c r="M180" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
     </row>
     <row r="181" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A181" s="2">
-        <v>545863368</v>
+        <v>620225240</v>
       </c>
       <c r="B181" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C181" s="2">
-        <v>8006540846063</v>
+        <v>8006540846186</v>
       </c>
       <c r="D181" t="s">
         <v>912</v>
       </c>
       <c r="E181" t="s">
-        <v>853</v>
+        <v>848</v>
       </c>
       <c r="F181" s="2"/>
       <c r="I181" t="s">
-        <v>854</v>
+        <v>849</v>
+      </c>
+      <c r="J181" t="s">
+        <v>850</v>
       </c>
       <c r="K181" t="s">
-        <v>846</v>
+        <v>851</v>
       </c>
       <c r="L181" t="s">
         <v>791</v>
       </c>
       <c r="M181" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
     </row>
     <row r="182" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A182" s="2">
-        <v>620225242</v>
+        <v>545863368</v>
       </c>
       <c r="B182" s="2">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="C182" s="2">
-        <v>8006540845677</v>
+        <v>8006540846063</v>
       </c>
       <c r="D182" t="s">
         <v>912</v>
       </c>
       <c r="E182" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="F182" s="2"/>
-      <c r="J182" t="s">
-        <v>857</v>
+      <c r="I182" t="s">
+        <v>854</v>
+      </c>
+      <c r="K182" t="s">
+        <v>846</v>
       </c>
       <c r="L182" t="s">
         <v>791</v>
       </c>
       <c r="M182" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
     </row>
     <row r="183" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A183" s="2">
-        <v>661215647</v>
+        <v>620225242</v>
       </c>
       <c r="B183" s="2">
-        <v>826</v>
+        <v>831</v>
       </c>
       <c r="C183" s="2">
-        <v>4210201355724</v>
+        <v>8006540845677</v>
       </c>
       <c r="D183" t="s">
         <v>912</v>
       </c>
       <c r="E183" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="F183" s="2"/>
-      <c r="I183" t="s">
-        <v>860</v>
-      </c>
       <c r="J183" t="s">
-        <v>861</v>
-      </c>
-      <c r="K183" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="L183" t="s">
         <v>791</v>
       </c>
       <c r="M183" t="s">
-        <v>904</v>
+        <v>858</v>
       </c>
     </row>
     <row r="184" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A184" s="2">
-        <v>130199415</v>
+        <v>661215647</v>
       </c>
       <c r="B184" s="2">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="C184" s="2">
-        <v>4210201360643</v>
+        <v>4210201355724</v>
       </c>
       <c r="D184" t="s">
         <v>912</v>
       </c>
       <c r="E184" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="F184" s="2"/>
+      <c r="I184" t="s">
+        <v>860</v>
+      </c>
       <c r="J184" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="K184" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="L184" t="s">
         <v>791</v>
       </c>
       <c r="M184" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="185" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A185" s="2">
-        <v>5923027</v>
+        <v>130199415</v>
       </c>
       <c r="B185" s="2">
-        <v>1004</v>
+        <v>834</v>
       </c>
       <c r="C185" s="2">
-        <v>4210201358633</v>
+        <v>4210201360643</v>
       </c>
       <c r="D185" t="s">
         <v>912</v>
       </c>
       <c r="E185" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="F185" s="2"/>
       <c r="J185" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="K185" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="L185" t="s">
         <v>791</v>
       </c>
       <c r="M185" t="s">
-        <v>869</v>
+        <v>905</v>
       </c>
     </row>
     <row r="186" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A186" s="2">
-        <v>4584425</v>
+        <v>5923027</v>
       </c>
       <c r="B186" s="2">
-        <v>832</v>
+        <v>1004</v>
       </c>
       <c r="C186" s="2">
-        <v>8006540846131</v>
+        <v>4210201358633</v>
       </c>
       <c r="D186" t="s">
         <v>912</v>
       </c>
       <c r="E186" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="F186" s="2"/>
-      <c r="I186" t="s">
-        <v>871</v>
+      <c r="J186" t="s">
+        <v>867</v>
+      </c>
+      <c r="K186" t="s">
+        <v>868</v>
       </c>
       <c r="L186" t="s">
         <v>791</v>
       </c>
       <c r="M186" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
     </row>
     <row r="187" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A187" s="2">
-        <v>703320509</v>
+        <v>4584425</v>
       </c>
       <c r="B187" s="2">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="C187" s="2">
-        <v>8006540846018</v>
+        <v>8006540846131</v>
       </c>
       <c r="D187" t="s">
         <v>912</v>
       </c>
       <c r="E187" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="F187" s="2"/>
+      <c r="I187" t="s">
+        <v>871</v>
+      </c>
       <c r="L187" t="s">
         <v>791</v>
       </c>
       <c r="M187" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
     </row>
     <row r="188" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A188" s="2">
-        <v>620422617</v>
+        <v>703320509</v>
       </c>
       <c r="B188" s="2">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="C188" s="2">
-        <v>8006540845851</v>
+        <v>8006540846018</v>
       </c>
       <c r="D188" t="s">
         <v>912</v>
       </c>
       <c r="E188" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="F188" s="2"/>
-      <c r="J188" t="s">
-        <v>876</v>
-      </c>
       <c r="L188" t="s">
         <v>791</v>
       </c>
       <c r="M188" t="s">
-        <v>906</v>
+        <v>874</v>
       </c>
     </row>
     <row r="189" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A189" s="2">
-        <v>620225236</v>
+        <v>620422617</v>
       </c>
       <c r="B189" s="2">
-        <v>828</v>
+        <v>833</v>
       </c>
       <c r="C189" s="2">
-        <v>8006540845721</v>
+        <v>8006540845851</v>
       </c>
       <c r="D189" t="s">
         <v>912</v>
       </c>
       <c r="E189" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="F189" s="2"/>
       <c r="J189" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="L189" t="s">
         <v>791</v>
       </c>
       <c r="M189" t="s">
-        <v>879</v>
+        <v>906</v>
       </c>
     </row>
     <row r="190" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A190" s="2">
-        <v>793320921</v>
+        <v>620225236</v>
       </c>
       <c r="B190" s="2">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="C190" s="2">
-        <v>8006540805251</v>
+        <v>8006540845721</v>
       </c>
       <c r="D190" t="s">
         <v>912</v>
       </c>
       <c r="E190" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="F190" s="2"/>
       <c r="J190" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="L190" t="s">
         <v>791</v>
       </c>
       <c r="M190" t="s">
-        <v>907</v>
+        <v>879</v>
       </c>
     </row>
     <row r="191" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A191" s="2">
-        <v>103019830</v>
+        <v>793320921</v>
       </c>
       <c r="B191" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C191" s="2">
-        <v>8006540804513</v>
+        <v>8006540805251</v>
       </c>
       <c r="D191" t="s">
         <v>912</v>
       </c>
       <c r="E191" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="F191" s="2"/>
       <c r="J191" t="s">
-        <v>883</v>
-      </c>
-      <c r="K191" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="L191" t="s">
         <v>791</v>
       </c>
       <c r="M191" t="s">
-        <v>885</v>
+        <v>907</v>
       </c>
     </row>
     <row r="192" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A192" s="2">
-        <v>509628692</v>
-      </c>
-      <c r="B192" s="2"/>
+        <v>103019830</v>
+      </c>
+      <c r="B192" s="2">
+        <v>824</v>
+      </c>
       <c r="C192" s="2">
-        <v>4210201355427</v>
+        <v>8006540804513</v>
       </c>
       <c r="D192" t="s">
         <v>912</v>
       </c>
       <c r="E192" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="F192" s="2"/>
-      <c r="I192" t="s">
-        <v>887</v>
+      <c r="J192" t="s">
+        <v>883</v>
+      </c>
+      <c r="K192" t="s">
+        <v>884</v>
       </c>
       <c r="L192" t="s">
         <v>791</v>
       </c>
       <c r="M192" t="s">
-        <v>888</v>
+        <v>885</v>
       </c>
     </row>
     <row r="193" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A193" s="2">
-        <v>593923</v>
-      </c>
-      <c r="B193" s="2">
-        <v>779</v>
-      </c>
+        <v>509628692</v>
+      </c>
+      <c r="B193" s="2"/>
       <c r="C193" s="2">
-        <v>4210201360247</v>
+        <v>4210201355427</v>
       </c>
       <c r="D193" t="s">
         <v>912</v>
       </c>
       <c r="E193" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="F193" s="2"/>
+      <c r="I193" t="s">
+        <v>887</v>
+      </c>
       <c r="L193" t="s">
         <v>791</v>
       </c>
       <c r="M193" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
     </row>
     <row r="194" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A194" s="2">
-        <v>140062</v>
+        <v>593923</v>
       </c>
       <c r="B194" s="2">
-        <v>828</v>
+        <v>779</v>
       </c>
       <c r="C194" s="2">
-        <v>4210201347149</v>
+        <v>4210201360247</v>
       </c>
       <c r="D194" t="s">
         <v>912</v>
       </c>
       <c r="E194" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="F194" s="2"/>
       <c r="L194" t="s">
         <v>791</v>
       </c>
       <c r="M194" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
     </row>
     <row r="195" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A195" s="2">
-        <v>551760014</v>
-      </c>
-      <c r="B195" s="2"/>
+        <v>140062</v>
+      </c>
+      <c r="B195" s="2">
+        <v>828</v>
+      </c>
       <c r="C195" s="2">
-        <v>4210201385615</v>
+        <v>4210201347149</v>
       </c>
       <c r="D195" t="s">
         <v>912</v>
       </c>
       <c r="E195" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="F195" s="2"/>
       <c r="L195" t="s">
         <v>791</v>
       </c>
       <c r="M195" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="196" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A196" s="2">
-        <v>61175622</v>
+        <v>551760014</v>
       </c>
       <c r="B196" s="2"/>
       <c r="C196" s="2">
-        <v>4210201387947</v>
+        <v>4210201385615</v>
       </c>
       <c r="D196" t="s">
         <v>912</v>
       </c>
       <c r="E196" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="F196" s="2"/>
       <c r="L196" t="s">
         <v>791</v>
       </c>
       <c r="M196" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="197" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A197" s="2">
+        <v>61175622</v>
+      </c>
+      <c r="B197" s="2"/>
+      <c r="C197" s="2">
+        <v>4210201387947</v>
+      </c>
+      <c r="D197" t="s">
+        <v>912</v>
+      </c>
+      <c r="E197" t="s">
+        <v>895</v>
+      </c>
+      <c r="F197" s="2"/>
+      <c r="L197" t="s">
+        <v>791</v>
+      </c>
+      <c r="M197" t="s">
         <v>896</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>